--- a/output/version3/test/20-10/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>796</v>
+        <v>863</v>
       </c>
       <c r="C2" t="n">
-        <v>986</v>
+        <v>798</v>
       </c>
       <c r="D2" t="n">
-        <v>933</v>
+        <v>991</v>
       </c>
       <c r="E2" t="n">
-        <v>1077</v>
+        <v>970</v>
       </c>
       <c r="F2" t="n">
-        <v>956</v>
+        <v>778</v>
       </c>
       <c r="G2" t="n">
-        <v>1102</v>
+        <v>957</v>
       </c>
       <c r="H2" t="n">
-        <v>921</v>
+        <v>848</v>
       </c>
       <c r="I2" t="n">
-        <v>1028</v>
+        <v>892</v>
       </c>
       <c r="J2" t="n">
-        <v>1068</v>
+        <v>889</v>
       </c>
       <c r="K2" t="n">
-        <v>930</v>
+        <v>848</v>
       </c>
       <c r="L2" t="n">
-        <v>979.7</v>
+        <v>883.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>937</v>
+        <v>972</v>
       </c>
       <c r="C3" t="n">
-        <v>775</v>
+        <v>868</v>
       </c>
       <c r="D3" t="n">
-        <v>949</v>
+        <v>1009</v>
       </c>
       <c r="E3" t="n">
-        <v>988</v>
+        <v>824</v>
       </c>
       <c r="F3" t="n">
-        <v>1026</v>
+        <v>924</v>
       </c>
       <c r="G3" t="n">
-        <v>795</v>
+        <v>926</v>
       </c>
       <c r="H3" t="n">
-        <v>932</v>
+        <v>902</v>
       </c>
       <c r="I3" t="n">
-        <v>864</v>
+        <v>897</v>
       </c>
       <c r="J3" t="n">
-        <v>956</v>
+        <v>840</v>
       </c>
       <c r="K3" t="n">
-        <v>876</v>
+        <v>930</v>
       </c>
       <c r="L3" t="n">
-        <v>909.8</v>
+        <v>909.2</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>772</v>
+        <v>826</v>
       </c>
       <c r="C4" t="n">
-        <v>922</v>
+        <v>896</v>
       </c>
       <c r="D4" t="n">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F4" t="n">
-        <v>802</v>
+        <v>878</v>
       </c>
       <c r="G4" t="n">
-        <v>986</v>
+        <v>852</v>
       </c>
       <c r="H4" t="n">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="I4" t="n">
-        <v>844</v>
+        <v>984</v>
       </c>
       <c r="J4" t="n">
-        <v>850</v>
+        <v>924</v>
       </c>
       <c r="K4" t="n">
-        <v>929</v>
+        <v>875</v>
       </c>
       <c r="L4" t="n">
-        <v>874.8</v>
+        <v>887.3</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>913</v>
+        <v>865</v>
       </c>
       <c r="C5" t="n">
-        <v>994</v>
+        <v>856</v>
       </c>
       <c r="D5" t="n">
-        <v>828</v>
+        <v>886</v>
       </c>
       <c r="E5" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F5" t="n">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="G5" t="n">
-        <v>877</v>
+        <v>947</v>
       </c>
       <c r="H5" t="n">
-        <v>798</v>
+        <v>840</v>
       </c>
       <c r="I5" t="n">
-        <v>815</v>
+        <v>930</v>
       </c>
       <c r="J5" t="n">
-        <v>767</v>
+        <v>839</v>
       </c>
       <c r="K5" t="n">
-        <v>739</v>
+        <v>893</v>
       </c>
       <c r="L5" t="n">
-        <v>846.7</v>
+        <v>876.8</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>957</v>
+        <v>870</v>
       </c>
       <c r="C6" t="n">
-        <v>872</v>
+        <v>966</v>
       </c>
       <c r="D6" t="n">
-        <v>810</v>
+        <v>774</v>
       </c>
       <c r="E6" t="n">
-        <v>825</v>
+        <v>885</v>
       </c>
       <c r="F6" t="n">
+        <v>822</v>
+      </c>
+      <c r="G6" t="n">
         <v>893</v>
       </c>
-      <c r="G6" t="n">
-        <v>825</v>
-      </c>
       <c r="H6" t="n">
-        <v>948</v>
+        <v>902</v>
       </c>
       <c r="I6" t="n">
-        <v>853</v>
+        <v>832</v>
       </c>
       <c r="J6" t="n">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="K6" t="n">
-        <v>818</v>
+        <v>982</v>
       </c>
       <c r="L6" t="n">
-        <v>866.3</v>
+        <v>877.5</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>924</v>
+        <v>811</v>
       </c>
       <c r="C7" t="n">
-        <v>794</v>
+        <v>860</v>
       </c>
       <c r="D7" t="n">
-        <v>927</v>
+        <v>876</v>
       </c>
       <c r="E7" t="n">
-        <v>795</v>
+        <v>818</v>
       </c>
       <c r="F7" t="n">
-        <v>812</v>
+        <v>929</v>
       </c>
       <c r="G7" t="n">
-        <v>894</v>
+        <v>1008</v>
       </c>
       <c r="H7" t="n">
-        <v>980</v>
+        <v>832</v>
       </c>
       <c r="I7" t="n">
-        <v>865</v>
+        <v>916</v>
       </c>
       <c r="J7" t="n">
-        <v>834</v>
+        <v>777</v>
       </c>
       <c r="K7" t="n">
-        <v>905</v>
+        <v>822</v>
       </c>
       <c r="L7" t="n">
-        <v>873</v>
+        <v>864.9</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1113</v>
+        <v>821</v>
       </c>
       <c r="C8" t="n">
-        <v>981</v>
+        <v>1025</v>
       </c>
       <c r="D8" t="n">
-        <v>882</v>
+        <v>965</v>
       </c>
       <c r="E8" t="n">
-        <v>861</v>
+        <v>906</v>
       </c>
       <c r="F8" t="n">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G8" t="n">
-        <v>932</v>
+        <v>976</v>
       </c>
       <c r="H8" t="n">
-        <v>870</v>
+        <v>917</v>
       </c>
       <c r="I8" t="n">
-        <v>944</v>
+        <v>878</v>
       </c>
       <c r="J8" t="n">
-        <v>944</v>
+        <v>963</v>
       </c>
       <c r="K8" t="n">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="L8" t="n">
-        <v>935.1</v>
+        <v>928.4</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>801</v>
+        <v>931</v>
       </c>
       <c r="C9" t="n">
-        <v>908</v>
+        <v>987</v>
       </c>
       <c r="D9" t="n">
-        <v>907</v>
+        <v>1019</v>
       </c>
       <c r="E9" t="n">
-        <v>975</v>
+        <v>887</v>
       </c>
       <c r="F9" t="n">
-        <v>913</v>
+        <v>860</v>
       </c>
       <c r="G9" t="n">
-        <v>813</v>
+        <v>880</v>
       </c>
       <c r="H9" t="n">
+        <v>879</v>
+      </c>
+      <c r="I9" t="n">
+        <v>799</v>
+      </c>
+      <c r="J9" t="n">
         <v>875</v>
       </c>
-      <c r="I9" t="n">
-        <v>838</v>
-      </c>
-      <c r="J9" t="n">
-        <v>983</v>
-      </c>
       <c r="K9" t="n">
-        <v>909</v>
+        <v>886</v>
       </c>
       <c r="L9" t="n">
-        <v>892.2</v>
+        <v>900.3</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>822</v>
+        <v>857</v>
       </c>
       <c r="C10" t="n">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D10" t="n">
-        <v>783</v>
+        <v>729</v>
       </c>
       <c r="E10" t="n">
-        <v>905</v>
+        <v>823</v>
       </c>
       <c r="F10" t="n">
-        <v>942</v>
+        <v>740</v>
       </c>
       <c r="G10" t="n">
-        <v>830</v>
+        <v>925</v>
       </c>
       <c r="H10" t="n">
-        <v>823</v>
+        <v>871</v>
       </c>
       <c r="I10" t="n">
-        <v>776</v>
+        <v>736</v>
       </c>
       <c r="J10" t="n">
-        <v>951</v>
+        <v>913</v>
       </c>
       <c r="K10" t="n">
-        <v>830</v>
+        <v>964</v>
       </c>
       <c r="L10" t="n">
-        <v>850.9</v>
+        <v>840.3</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>722</v>
+        <v>825</v>
       </c>
       <c r="C11" t="n">
-        <v>764</v>
+        <v>954</v>
       </c>
       <c r="D11" t="n">
-        <v>753</v>
+        <v>801</v>
       </c>
       <c r="E11" t="n">
-        <v>893</v>
+        <v>799</v>
       </c>
       <c r="F11" t="n">
-        <v>929</v>
+        <v>865</v>
       </c>
       <c r="G11" t="n">
-        <v>837</v>
+        <v>785</v>
       </c>
       <c r="H11" t="n">
-        <v>768</v>
+        <v>902</v>
       </c>
       <c r="I11" t="n">
-        <v>978</v>
+        <v>844</v>
       </c>
       <c r="J11" t="n">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="K11" t="n">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="L11" t="n">
-        <v>840.5</v>
+        <v>852.9</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>943</v>
+        <v>830</v>
       </c>
       <c r="C12" t="n">
-        <v>939</v>
+        <v>887</v>
       </c>
       <c r="D12" t="n">
-        <v>868</v>
+        <v>800</v>
       </c>
       <c r="E12" t="n">
-        <v>888</v>
+        <v>904</v>
       </c>
       <c r="F12" t="n">
-        <v>930</v>
+        <v>839</v>
       </c>
       <c r="G12" t="n">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="H12" t="n">
-        <v>810</v>
+        <v>929</v>
       </c>
       <c r="I12" t="n">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="J12" t="n">
-        <v>850</v>
+        <v>940</v>
       </c>
       <c r="K12" t="n">
-        <v>896</v>
+        <v>883</v>
       </c>
       <c r="L12" t="n">
-        <v>887.6</v>
+        <v>876.9</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>929</v>
+        <v>873</v>
       </c>
       <c r="C13" t="n">
-        <v>1080</v>
+        <v>803</v>
       </c>
       <c r="D13" t="n">
-        <v>948</v>
+        <v>818</v>
       </c>
       <c r="E13" t="n">
-        <v>1021</v>
+        <v>938</v>
       </c>
       <c r="F13" t="n">
-        <v>942</v>
+        <v>828</v>
       </c>
       <c r="G13" t="n">
-        <v>928</v>
+        <v>837</v>
       </c>
       <c r="H13" t="n">
-        <v>786</v>
+        <v>869</v>
       </c>
       <c r="I13" t="n">
-        <v>850</v>
+        <v>884</v>
       </c>
       <c r="J13" t="n">
-        <v>825</v>
+        <v>934</v>
       </c>
       <c r="K13" t="n">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="L13" t="n">
-        <v>922.6</v>
+        <v>868.8</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="C14" t="n">
-        <v>937</v>
+        <v>922</v>
       </c>
       <c r="D14" t="n">
-        <v>921</v>
+        <v>1080</v>
       </c>
       <c r="E14" t="n">
-        <v>979</v>
+        <v>849</v>
       </c>
       <c r="F14" t="n">
-        <v>904</v>
+        <v>998</v>
       </c>
       <c r="G14" t="n">
-        <v>812</v>
+        <v>949</v>
       </c>
       <c r="H14" t="n">
-        <v>832</v>
+        <v>923</v>
       </c>
       <c r="I14" t="n">
-        <v>930</v>
+        <v>797</v>
       </c>
       <c r="J14" t="n">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="K14" t="n">
-        <v>905</v>
+        <v>858</v>
       </c>
       <c r="L14" t="n">
-        <v>908.7</v>
+        <v>922</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>966</v>
+        <v>841</v>
       </c>
       <c r="C15" t="n">
-        <v>951</v>
+        <v>895</v>
       </c>
       <c r="D15" t="n">
+        <v>896</v>
+      </c>
+      <c r="E15" t="n">
+        <v>952</v>
+      </c>
+      <c r="F15" t="n">
+        <v>957</v>
+      </c>
+      <c r="G15" t="n">
+        <v>917</v>
+      </c>
+      <c r="H15" t="n">
+        <v>888</v>
+      </c>
+      <c r="I15" t="n">
+        <v>848</v>
+      </c>
+      <c r="J15" t="n">
         <v>1044</v>
       </c>
-      <c r="E15" t="n">
-        <v>961</v>
-      </c>
-      <c r="F15" t="n">
-        <v>863</v>
-      </c>
-      <c r="G15" t="n">
-        <v>951</v>
-      </c>
-      <c r="H15" t="n">
-        <v>895</v>
-      </c>
-      <c r="I15" t="n">
-        <v>830</v>
-      </c>
-      <c r="J15" t="n">
-        <v>957</v>
-      </c>
       <c r="K15" t="n">
-        <v>817</v>
+        <v>996</v>
       </c>
       <c r="L15" t="n">
-        <v>923.5</v>
+        <v>923.4</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>982</v>
+        <v>898</v>
       </c>
       <c r="C16" t="n">
-        <v>825</v>
+        <v>801</v>
       </c>
       <c r="D16" t="n">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E16" t="n">
-        <v>942</v>
+        <v>1129</v>
       </c>
       <c r="F16" t="n">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="G16" t="n">
-        <v>931</v>
+        <v>828</v>
       </c>
       <c r="H16" t="n">
-        <v>902</v>
+        <v>818</v>
       </c>
       <c r="I16" t="n">
-        <v>1015</v>
+        <v>941</v>
       </c>
       <c r="J16" t="n">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="K16" t="n">
-        <v>876</v>
+        <v>922</v>
       </c>
       <c r="L16" t="n">
-        <v>910.2</v>
+        <v>898.3</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>914</v>
+        <v>764</v>
       </c>
       <c r="C17" t="n">
-        <v>830</v>
+        <v>785</v>
       </c>
       <c r="D17" t="n">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="E17" t="n">
-        <v>854</v>
+        <v>810</v>
       </c>
       <c r="F17" t="n">
-        <v>719</v>
+        <v>899</v>
       </c>
       <c r="G17" t="n">
-        <v>780</v>
+        <v>851</v>
       </c>
       <c r="H17" t="n">
-        <v>808</v>
+        <v>698</v>
       </c>
       <c r="I17" t="n">
-        <v>743</v>
+        <v>831</v>
       </c>
       <c r="J17" t="n">
-        <v>699</v>
+        <v>881</v>
       </c>
       <c r="K17" t="n">
-        <v>794</v>
+        <v>724</v>
       </c>
       <c r="L17" t="n">
-        <v>795.3</v>
+        <v>806.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>958</v>
+        <v>933</v>
       </c>
       <c r="C18" t="n">
-        <v>891</v>
+        <v>860</v>
       </c>
       <c r="D18" t="n">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="E18" t="n">
-        <v>952</v>
+        <v>918</v>
       </c>
       <c r="F18" t="n">
-        <v>924</v>
+        <v>911</v>
       </c>
       <c r="G18" t="n">
-        <v>980</v>
+        <v>1007</v>
       </c>
       <c r="H18" t="n">
-        <v>952</v>
+        <v>884</v>
       </c>
       <c r="I18" t="n">
-        <v>982</v>
+        <v>1085</v>
       </c>
       <c r="J18" t="n">
-        <v>983</v>
+        <v>936</v>
       </c>
       <c r="K18" t="n">
-        <v>827</v>
+        <v>988</v>
       </c>
       <c r="L18" t="n">
-        <v>942.6</v>
+        <v>950.6</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C19" t="n">
-        <v>791</v>
+        <v>708</v>
       </c>
       <c r="D19" t="n">
-        <v>800</v>
+        <v>778</v>
       </c>
       <c r="E19" t="n">
-        <v>910</v>
+        <v>767</v>
       </c>
       <c r="F19" t="n">
-        <v>923</v>
+        <v>692</v>
       </c>
       <c r="G19" t="n">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="H19" t="n">
-        <v>965</v>
+        <v>872</v>
       </c>
       <c r="I19" t="n">
-        <v>867</v>
+        <v>892</v>
       </c>
       <c r="J19" t="n">
-        <v>936</v>
+        <v>829</v>
       </c>
       <c r="K19" t="n">
-        <v>764</v>
+        <v>833</v>
       </c>
       <c r="L19" t="n">
-        <v>841.7</v>
+        <v>784.5</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>907</v>
+        <v>735</v>
       </c>
       <c r="C20" t="n">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="D20" t="n">
-        <v>781</v>
+        <v>922</v>
       </c>
       <c r="E20" t="n">
-        <v>776</v>
+        <v>829</v>
       </c>
       <c r="F20" t="n">
-        <v>773</v>
+        <v>713</v>
       </c>
       <c r="G20" t="n">
-        <v>778</v>
+        <v>808</v>
       </c>
       <c r="H20" t="n">
-        <v>838</v>
+        <v>753</v>
       </c>
       <c r="I20" t="n">
-        <v>887</v>
+        <v>741</v>
       </c>
       <c r="J20" t="n">
-        <v>790</v>
+        <v>753</v>
       </c>
       <c r="K20" t="n">
-        <v>804</v>
+        <v>759</v>
       </c>
       <c r="L20" t="n">
-        <v>808.1</v>
+        <v>777</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>802</v>
+        <v>914</v>
       </c>
       <c r="C21" t="n">
-        <v>822</v>
+        <v>1049</v>
       </c>
       <c r="D21" t="n">
-        <v>1014</v>
+        <v>1028</v>
       </c>
       <c r="E21" t="n">
-        <v>847</v>
+        <v>825</v>
       </c>
       <c r="F21" t="n">
-        <v>979</v>
+        <v>958</v>
       </c>
       <c r="G21" t="n">
-        <v>942</v>
+        <v>837</v>
       </c>
       <c r="H21" t="n">
-        <v>965</v>
+        <v>767</v>
       </c>
       <c r="I21" t="n">
-        <v>856</v>
+        <v>837</v>
       </c>
       <c r="J21" t="n">
-        <v>838</v>
+        <v>908</v>
       </c>
       <c r="K21" t="n">
-        <v>991</v>
+        <v>889</v>
       </c>
       <c r="L21" t="n">
-        <v>905.6</v>
+        <v>901.2</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>975</v>
+        <v>879</v>
       </c>
       <c r="C22" t="n">
-        <v>854</v>
+        <v>830</v>
       </c>
       <c r="D22" t="n">
-        <v>986</v>
+        <v>833</v>
       </c>
       <c r="E22" t="n">
-        <v>888</v>
+        <v>961</v>
       </c>
       <c r="F22" t="n">
-        <v>854</v>
+        <v>870</v>
       </c>
       <c r="G22" t="n">
-        <v>871</v>
+        <v>928</v>
       </c>
       <c r="H22" t="n">
-        <v>1073</v>
+        <v>880</v>
       </c>
       <c r="I22" t="n">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="J22" t="n">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="K22" t="n">
-        <v>915</v>
+        <v>853</v>
       </c>
       <c r="L22" t="n">
-        <v>919.2</v>
+        <v>880.7</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>857</v>
+        <v>910</v>
       </c>
       <c r="C23" t="n">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D23" t="n">
-        <v>913</v>
+        <v>1027</v>
       </c>
       <c r="E23" t="n">
-        <v>834</v>
+        <v>878</v>
       </c>
       <c r="F23" t="n">
-        <v>894</v>
+        <v>924</v>
       </c>
       <c r="G23" t="n">
-        <v>926</v>
+        <v>848</v>
       </c>
       <c r="H23" t="n">
-        <v>839</v>
+        <v>924</v>
       </c>
       <c r="I23" t="n">
-        <v>923</v>
+        <v>953</v>
       </c>
       <c r="J23" t="n">
-        <v>958</v>
+        <v>888</v>
       </c>
       <c r="K23" t="n">
-        <v>883</v>
+        <v>851</v>
       </c>
       <c r="L23" t="n">
-        <v>893</v>
+        <v>910.9</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>782</v>
+        <v>830</v>
       </c>
       <c r="C24" t="n">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="D24" t="n">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="E24" t="n">
-        <v>863</v>
+        <v>816</v>
       </c>
       <c r="F24" t="n">
-        <v>860</v>
+        <v>832</v>
       </c>
       <c r="G24" t="n">
-        <v>844</v>
+        <v>927</v>
       </c>
       <c r="H24" t="n">
-        <v>719</v>
+        <v>838</v>
       </c>
       <c r="I24" t="n">
-        <v>818</v>
+        <v>727</v>
       </c>
       <c r="J24" t="n">
-        <v>929</v>
+        <v>767</v>
       </c>
       <c r="K24" t="n">
-        <v>973</v>
+        <v>898</v>
       </c>
       <c r="L24" t="n">
-        <v>846.1</v>
+        <v>834.2</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>934</v>
+        <v>973</v>
       </c>
       <c r="C25" t="n">
-        <v>785</v>
+        <v>872</v>
       </c>
       <c r="D25" t="n">
-        <v>916</v>
+        <v>931</v>
       </c>
       <c r="E25" t="n">
-        <v>937</v>
+        <v>890</v>
       </c>
       <c r="F25" t="n">
         <v>873</v>
       </c>
       <c r="G25" t="n">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="H25" t="n">
-        <v>869</v>
+        <v>816</v>
       </c>
       <c r="I25" t="n">
-        <v>887</v>
+        <v>826</v>
       </c>
       <c r="J25" t="n">
-        <v>970</v>
+        <v>814</v>
       </c>
       <c r="K25" t="n">
-        <v>848</v>
+        <v>877</v>
       </c>
       <c r="L25" t="n">
-        <v>887</v>
+        <v>873.4</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1076</v>
+        <v>970</v>
       </c>
       <c r="C26" t="n">
-        <v>986</v>
+        <v>929</v>
       </c>
       <c r="D26" t="n">
-        <v>956</v>
+        <v>1009</v>
       </c>
       <c r="E26" t="n">
-        <v>1036</v>
+        <v>985</v>
       </c>
       <c r="F26" t="n">
-        <v>854</v>
+        <v>897</v>
       </c>
       <c r="G26" t="n">
-        <v>893</v>
+        <v>916</v>
       </c>
       <c r="H26" t="n">
-        <v>979</v>
+        <v>856</v>
       </c>
       <c r="I26" t="n">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="J26" t="n">
-        <v>942</v>
+        <v>1029</v>
       </c>
       <c r="K26" t="n">
-        <v>974</v>
+        <v>860</v>
       </c>
       <c r="L26" t="n">
-        <v>962.3</v>
+        <v>937.4</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>824</v>
+        <v>920</v>
       </c>
       <c r="C27" t="n">
-        <v>829</v>
+        <v>1041</v>
       </c>
       <c r="D27" t="n">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="E27" t="n">
-        <v>884</v>
+        <v>983</v>
       </c>
       <c r="F27" t="n">
-        <v>985</v>
+        <v>938</v>
       </c>
       <c r="G27" t="n">
-        <v>966</v>
+        <v>1055</v>
       </c>
       <c r="H27" t="n">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="I27" t="n">
-        <v>932</v>
+        <v>986</v>
       </c>
       <c r="J27" t="n">
-        <v>964</v>
+        <v>934</v>
       </c>
       <c r="K27" t="n">
-        <v>1005</v>
+        <v>869</v>
       </c>
       <c r="L27" t="n">
-        <v>925.8</v>
+        <v>958.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>814</v>
+        <v>750</v>
       </c>
       <c r="C28" t="n">
-        <v>744</v>
+        <v>911</v>
       </c>
       <c r="D28" t="n">
-        <v>828</v>
+        <v>813</v>
       </c>
       <c r="E28" t="n">
-        <v>838</v>
+        <v>885</v>
       </c>
       <c r="F28" t="n">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="G28" t="n">
-        <v>872</v>
+        <v>833</v>
       </c>
       <c r="H28" t="n">
-        <v>837</v>
+        <v>802</v>
       </c>
       <c r="I28" t="n">
-        <v>790</v>
+        <v>752</v>
       </c>
       <c r="J28" t="n">
-        <v>812</v>
+        <v>845</v>
       </c>
       <c r="K28" t="n">
-        <v>752</v>
+        <v>869</v>
       </c>
       <c r="L28" t="n">
-        <v>804.6</v>
+        <v>821</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>830</v>
+        <v>783</v>
       </c>
       <c r="C29" t="n">
-        <v>927</v>
+        <v>852</v>
       </c>
       <c r="D29" t="n">
+        <v>913</v>
+      </c>
+      <c r="E29" t="n">
+        <v>861</v>
+      </c>
+      <c r="F29" t="n">
+        <v>757</v>
+      </c>
+      <c r="G29" t="n">
+        <v>788</v>
+      </c>
+      <c r="H29" t="n">
+        <v>917</v>
+      </c>
+      <c r="I29" t="n">
+        <v>837</v>
+      </c>
+      <c r="J29" t="n">
         <v>848</v>
       </c>
-      <c r="E29" t="n">
-        <v>860</v>
-      </c>
-      <c r="F29" t="n">
-        <v>826</v>
-      </c>
-      <c r="G29" t="n">
-        <v>864</v>
-      </c>
-      <c r="H29" t="n">
-        <v>875</v>
-      </c>
-      <c r="I29" t="n">
-        <v>815</v>
-      </c>
-      <c r="J29" t="n">
-        <v>763</v>
-      </c>
       <c r="K29" t="n">
-        <v>792</v>
+        <v>766</v>
       </c>
       <c r="L29" t="n">
-        <v>840</v>
+        <v>832.2</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>949</v>
+        <v>907</v>
       </c>
       <c r="C30" t="n">
-        <v>870</v>
+        <v>826</v>
       </c>
       <c r="D30" t="n">
-        <v>819</v>
+        <v>929</v>
       </c>
       <c r="E30" t="n">
-        <v>819</v>
+        <v>861</v>
       </c>
       <c r="F30" t="n">
-        <v>985</v>
+        <v>814</v>
       </c>
       <c r="G30" t="n">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="H30" t="n">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="I30" t="n">
-        <v>830</v>
+        <v>803</v>
       </c>
       <c r="J30" t="n">
-        <v>855</v>
+        <v>871</v>
       </c>
       <c r="K30" t="n">
-        <v>882</v>
+        <v>782</v>
       </c>
       <c r="L30" t="n">
-        <v>872.1</v>
+        <v>848.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>982</v>
+        <v>1025</v>
       </c>
       <c r="C31" t="n">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="D31" t="n">
-        <v>970</v>
+        <v>1011</v>
       </c>
       <c r="E31" t="n">
+        <v>847</v>
+      </c>
+      <c r="F31" t="n">
+        <v>945</v>
+      </c>
+      <c r="G31" t="n">
+        <v>882</v>
+      </c>
+      <c r="H31" t="n">
+        <v>816</v>
+      </c>
+      <c r="I31" t="n">
+        <v>879</v>
+      </c>
+      <c r="J31" t="n">
         <v>947</v>
       </c>
-      <c r="F31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1022</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1038</v>
-      </c>
-      <c r="I31" t="n">
-        <v>877</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1019</v>
-      </c>
       <c r="K31" t="n">
-        <v>1047</v>
+        <v>841</v>
       </c>
       <c r="L31" t="n">
-        <v>980.5</v>
+        <v>912.6</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>922</v>
+        <v>962</v>
       </c>
       <c r="C32" t="n">
-        <v>919</v>
+        <v>956</v>
       </c>
       <c r="D32" t="n">
-        <v>950</v>
+        <v>1019</v>
       </c>
       <c r="E32" t="n">
-        <v>991</v>
+        <v>1013</v>
       </c>
       <c r="F32" t="n">
-        <v>1106</v>
+        <v>1039</v>
       </c>
       <c r="G32" t="n">
-        <v>933</v>
+        <v>973</v>
       </c>
       <c r="H32" t="n">
-        <v>1011</v>
+        <v>1043</v>
       </c>
       <c r="I32" t="n">
-        <v>1109</v>
+        <v>910</v>
       </c>
       <c r="J32" t="n">
-        <v>864</v>
+        <v>1140</v>
       </c>
       <c r="K32" t="n">
-        <v>919</v>
+        <v>1023</v>
       </c>
       <c r="L32" t="n">
-        <v>972.4</v>
+        <v>1007.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>830</v>
+        <v>931</v>
       </c>
       <c r="C33" t="n">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="D33" t="n">
-        <v>844</v>
+        <v>926</v>
       </c>
       <c r="E33" t="n">
-        <v>823</v>
+        <v>911</v>
       </c>
       <c r="F33" t="n">
-        <v>1029</v>
+        <v>890</v>
       </c>
       <c r="G33" t="n">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="H33" t="n">
-        <v>951</v>
+        <v>903</v>
       </c>
       <c r="I33" t="n">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="J33" t="n">
-        <v>808</v>
+        <v>965</v>
       </c>
       <c r="K33" t="n">
-        <v>965</v>
+        <v>912</v>
       </c>
       <c r="L33" t="n">
-        <v>884.2</v>
+        <v>905.3</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>848</v>
+        <v>857</v>
       </c>
       <c r="C34" t="n">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="D34" t="n">
-        <v>888</v>
+        <v>950</v>
       </c>
       <c r="E34" t="n">
-        <v>911</v>
+        <v>830</v>
       </c>
       <c r="F34" t="n">
-        <v>845</v>
+        <v>986</v>
       </c>
       <c r="G34" t="n">
-        <v>856</v>
+        <v>906</v>
       </c>
       <c r="H34" t="n">
-        <v>977</v>
+        <v>878</v>
       </c>
       <c r="I34" t="n">
-        <v>995</v>
+        <v>916</v>
       </c>
       <c r="J34" t="n">
-        <v>960</v>
+        <v>1032</v>
       </c>
       <c r="K34" t="n">
-        <v>967</v>
+        <v>976</v>
       </c>
       <c r="L34" t="n">
-        <v>909.6</v>
+        <v>917.2</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="C35" t="n">
-        <v>998</v>
+        <v>887</v>
       </c>
       <c r="D35" t="n">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="E35" t="n">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="F35" t="n">
-        <v>980</v>
+        <v>861</v>
       </c>
       <c r="G35" t="n">
-        <v>918</v>
+        <v>958</v>
       </c>
       <c r="H35" t="n">
-        <v>978</v>
+        <v>896</v>
       </c>
       <c r="I35" t="n">
-        <v>882</v>
+        <v>1151</v>
       </c>
       <c r="J35" t="n">
-        <v>944</v>
+        <v>961</v>
       </c>
       <c r="K35" t="n">
-        <v>852</v>
+        <v>970</v>
       </c>
       <c r="L35" t="n">
-        <v>939.1</v>
+        <v>950.3</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>909</v>
+        <v>1073</v>
       </c>
       <c r="C36" t="n">
-        <v>892</v>
+        <v>960</v>
       </c>
       <c r="D36" t="n">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="E36" t="n">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="F36" t="n">
-        <v>966</v>
+        <v>914</v>
       </c>
       <c r="G36" t="n">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H36" t="n">
-        <v>907</v>
+        <v>992</v>
       </c>
       <c r="I36" t="n">
-        <v>822</v>
+        <v>956</v>
       </c>
       <c r="J36" t="n">
-        <v>782</v>
+        <v>805</v>
       </c>
       <c r="K36" t="n">
-        <v>1066</v>
+        <v>936</v>
       </c>
       <c r="L36" t="n">
-        <v>910.3</v>
+        <v>939.5</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="C37" t="n">
-        <v>914</v>
+        <v>886</v>
       </c>
       <c r="D37" t="n">
+        <v>900</v>
+      </c>
+      <c r="E37" t="n">
+        <v>826</v>
+      </c>
+      <c r="F37" t="n">
+        <v>897</v>
+      </c>
+      <c r="G37" t="n">
         <v>835</v>
       </c>
-      <c r="E37" t="n">
-        <v>839</v>
-      </c>
-      <c r="F37" t="n">
-        <v>961</v>
-      </c>
-      <c r="G37" t="n">
-        <v>824</v>
-      </c>
       <c r="H37" t="n">
-        <v>771</v>
+        <v>806</v>
       </c>
       <c r="I37" t="n">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="J37" t="n">
-        <v>921</v>
+        <v>893</v>
       </c>
       <c r="K37" t="n">
-        <v>850</v>
+        <v>869</v>
       </c>
       <c r="L37" t="n">
-        <v>869.6</v>
+        <v>868.8</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>833</v>
+        <v>777</v>
       </c>
       <c r="C38" t="n">
-        <v>741</v>
+        <v>790</v>
       </c>
       <c r="D38" t="n">
-        <v>800</v>
+        <v>813</v>
       </c>
       <c r="E38" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="F38" t="n">
-        <v>760</v>
+        <v>915</v>
       </c>
       <c r="G38" t="n">
-        <v>852</v>
+        <v>824</v>
       </c>
       <c r="H38" t="n">
-        <v>919</v>
+        <v>831</v>
       </c>
       <c r="I38" t="n">
-        <v>930</v>
+        <v>758</v>
       </c>
       <c r="J38" t="n">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K38" t="n">
-        <v>762</v>
+        <v>817</v>
       </c>
       <c r="L38" t="n">
-        <v>818.9</v>
+        <v>806.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>799</v>
+        <v>855</v>
       </c>
       <c r="C39" t="n">
-        <v>755</v>
+        <v>884</v>
       </c>
       <c r="D39" t="n">
-        <v>847</v>
+        <v>955</v>
       </c>
       <c r="E39" t="n">
-        <v>846</v>
+        <v>963</v>
       </c>
       <c r="F39" t="n">
-        <v>894</v>
+        <v>945</v>
       </c>
       <c r="G39" t="n">
-        <v>776</v>
+        <v>859</v>
       </c>
       <c r="H39" t="n">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="I39" t="n">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="J39" t="n">
-        <v>864</v>
+        <v>954</v>
       </c>
       <c r="K39" t="n">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="L39" t="n">
-        <v>835.5</v>
+        <v>899.9</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>923</v>
+        <v>730</v>
       </c>
       <c r="C40" t="n">
-        <v>748</v>
+        <v>847</v>
       </c>
       <c r="D40" t="n">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="E40" t="n">
-        <v>863</v>
+        <v>819</v>
       </c>
       <c r="F40" t="n">
-        <v>781</v>
+        <v>841</v>
       </c>
       <c r="G40" t="n">
-        <v>890</v>
+        <v>920</v>
       </c>
       <c r="H40" t="n">
-        <v>862</v>
+        <v>793</v>
       </c>
       <c r="I40" t="n">
-        <v>830</v>
+        <v>741</v>
       </c>
       <c r="J40" t="n">
-        <v>862</v>
+        <v>790</v>
       </c>
       <c r="K40" t="n">
-        <v>782</v>
+        <v>883</v>
       </c>
       <c r="L40" t="n">
-        <v>839.1</v>
+        <v>820.9</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>967</v>
+        <v>770</v>
       </c>
       <c r="C41" t="n">
-        <v>965</v>
+        <v>827</v>
       </c>
       <c r="D41" t="n">
-        <v>885</v>
+        <v>750</v>
       </c>
       <c r="E41" t="n">
-        <v>878</v>
+        <v>785</v>
       </c>
       <c r="F41" t="n">
+        <v>995</v>
+      </c>
+      <c r="G41" t="n">
+        <v>809</v>
+      </c>
+      <c r="H41" t="n">
+        <v>758</v>
+      </c>
+      <c r="I41" t="n">
+        <v>790</v>
+      </c>
+      <c r="J41" t="n">
+        <v>814</v>
+      </c>
+      <c r="K41" t="n">
         <v>796</v>
       </c>
-      <c r="G41" t="n">
-        <v>846</v>
-      </c>
-      <c r="H41" t="n">
-        <v>813</v>
-      </c>
-      <c r="I41" t="n">
-        <v>818</v>
-      </c>
-      <c r="J41" t="n">
-        <v>738</v>
-      </c>
-      <c r="K41" t="n">
-        <v>783</v>
-      </c>
       <c r="L41" t="n">
-        <v>848.9</v>
+        <v>809.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>890</v>
+        <v>809</v>
       </c>
       <c r="C42" t="n">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D42" t="n">
-        <v>856</v>
+        <v>776</v>
       </c>
       <c r="E42" t="n">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="F42" t="n">
-        <v>935</v>
+        <v>826</v>
       </c>
       <c r="G42" t="n">
-        <v>911</v>
+        <v>848</v>
       </c>
       <c r="H42" t="n">
-        <v>855</v>
+        <v>807</v>
       </c>
       <c r="I42" t="n">
-        <v>833</v>
+        <v>984</v>
       </c>
       <c r="J42" t="n">
-        <v>915</v>
+        <v>741</v>
       </c>
       <c r="K42" t="n">
-        <v>792</v>
+        <v>824</v>
       </c>
       <c r="L42" t="n">
-        <v>869.3</v>
+        <v>832.6</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>813</v>
+        <v>918</v>
       </c>
       <c r="C43" t="n">
-        <v>867</v>
+        <v>903</v>
       </c>
       <c r="D43" t="n">
-        <v>887</v>
+        <v>802</v>
       </c>
       <c r="E43" t="n">
-        <v>798</v>
+        <v>855</v>
       </c>
       <c r="F43" t="n">
-        <v>788</v>
+        <v>815</v>
       </c>
       <c r="G43" t="n">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="H43" t="n">
-        <v>913</v>
+        <v>830</v>
       </c>
       <c r="I43" t="n">
-        <v>945</v>
+        <v>831</v>
       </c>
       <c r="J43" t="n">
-        <v>819</v>
+        <v>1015</v>
       </c>
       <c r="K43" t="n">
-        <v>1005</v>
+        <v>854</v>
       </c>
       <c r="L43" t="n">
-        <v>862.9</v>
+        <v>861.9</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>796</v>
+        <v>734</v>
       </c>
       <c r="C44" t="n">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D44" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="E44" t="n">
-        <v>817</v>
+        <v>893</v>
       </c>
       <c r="F44" t="n">
-        <v>756</v>
+        <v>831</v>
       </c>
       <c r="G44" t="n">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="H44" t="n">
-        <v>735</v>
+        <v>830</v>
       </c>
       <c r="I44" t="n">
-        <v>799</v>
+        <v>858</v>
       </c>
       <c r="J44" t="n">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="K44" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="L44" t="n">
-        <v>765.1</v>
+        <v>783.6</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="C45" t="n">
-        <v>1072</v>
+        <v>960</v>
       </c>
       <c r="D45" t="n">
-        <v>1009</v>
+        <v>1085</v>
       </c>
       <c r="E45" t="n">
-        <v>1017</v>
+        <v>1047</v>
       </c>
       <c r="F45" t="n">
-        <v>952</v>
+        <v>899</v>
       </c>
       <c r="G45" t="n">
-        <v>922</v>
+        <v>956</v>
       </c>
       <c r="H45" t="n">
-        <v>1049</v>
+        <v>1115</v>
       </c>
       <c r="I45" t="n">
-        <v>898</v>
+        <v>1010</v>
       </c>
       <c r="J45" t="n">
-        <v>1077</v>
+        <v>1011</v>
       </c>
       <c r="K45" t="n">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="L45" t="n">
-        <v>1004</v>
+        <v>1011.9</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>879</v>
+        <v>853</v>
       </c>
       <c r="C46" t="n">
-        <v>880</v>
+        <v>833</v>
       </c>
       <c r="D46" t="n">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="E46" t="n">
-        <v>1020</v>
+        <v>876</v>
       </c>
       <c r="F46" t="n">
-        <v>837</v>
+        <v>865</v>
       </c>
       <c r="G46" t="n">
-        <v>854</v>
+        <v>805</v>
       </c>
       <c r="H46" t="n">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="I46" t="n">
-        <v>963</v>
+        <v>803</v>
       </c>
       <c r="J46" t="n">
-        <v>858</v>
+        <v>831</v>
       </c>
       <c r="K46" t="n">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="L46" t="n">
-        <v>892.9</v>
+        <v>851.4</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>957</v>
+        <v>897</v>
       </c>
       <c r="C47" t="n">
-        <v>966</v>
+        <v>891</v>
       </c>
       <c r="D47" t="n">
-        <v>1011</v>
+        <v>1168</v>
       </c>
       <c r="E47" t="n">
-        <v>1034</v>
+        <v>967</v>
       </c>
       <c r="F47" t="n">
-        <v>880</v>
+        <v>859</v>
       </c>
       <c r="G47" t="n">
-        <v>860</v>
+        <v>992</v>
       </c>
       <c r="H47" t="n">
-        <v>1135</v>
+        <v>894</v>
       </c>
       <c r="I47" t="n">
-        <v>876</v>
+        <v>977</v>
       </c>
       <c r="J47" t="n">
-        <v>1008</v>
+        <v>973</v>
       </c>
       <c r="K47" t="n">
-        <v>838</v>
+        <v>953</v>
       </c>
       <c r="L47" t="n">
-        <v>956.5</v>
+        <v>957.1</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>814</v>
+        <v>790</v>
       </c>
       <c r="C48" t="n">
-        <v>718</v>
+        <v>842</v>
       </c>
       <c r="D48" t="n">
-        <v>972</v>
+        <v>694</v>
       </c>
       <c r="E48" t="n">
-        <v>744</v>
+        <v>788</v>
       </c>
       <c r="F48" t="n">
-        <v>706</v>
+        <v>802</v>
       </c>
       <c r="G48" t="n">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="H48" t="n">
-        <v>683</v>
+        <v>703</v>
       </c>
       <c r="I48" t="n">
-        <v>738</v>
+        <v>883</v>
       </c>
       <c r="J48" t="n">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="K48" t="n">
-        <v>703</v>
+        <v>861</v>
       </c>
       <c r="L48" t="n">
-        <v>756.2</v>
+        <v>789.3</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>944</v>
+        <v>779</v>
       </c>
       <c r="C49" t="n">
-        <v>1015</v>
+        <v>938</v>
       </c>
       <c r="D49" t="n">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E49" t="n">
-        <v>851</v>
+        <v>905</v>
       </c>
       <c r="F49" t="n">
-        <v>789</v>
+        <v>849</v>
       </c>
       <c r="G49" t="n">
-        <v>903</v>
+        <v>860</v>
       </c>
       <c r="H49" t="n">
-        <v>853</v>
+        <v>813</v>
       </c>
       <c r="I49" t="n">
-        <v>768</v>
+        <v>972</v>
       </c>
       <c r="J49" t="n">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="K49" t="n">
-        <v>822</v>
+        <v>916</v>
       </c>
       <c r="L49" t="n">
-        <v>867.6</v>
+        <v>874.7</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>905</v>
+        <v>987</v>
       </c>
       <c r="C50" t="n">
-        <v>869</v>
+        <v>819</v>
       </c>
       <c r="D50" t="n">
-        <v>842</v>
+        <v>751</v>
       </c>
       <c r="E50" t="n">
-        <v>903</v>
+        <v>849</v>
       </c>
       <c r="F50" t="n">
-        <v>991</v>
+        <v>847</v>
       </c>
       <c r="G50" t="n">
-        <v>887</v>
+        <v>806</v>
       </c>
       <c r="H50" t="n">
-        <v>905</v>
+        <v>814</v>
       </c>
       <c r="I50" t="n">
-        <v>846</v>
+        <v>910</v>
       </c>
       <c r="J50" t="n">
-        <v>765</v>
+        <v>1151</v>
       </c>
       <c r="K50" t="n">
-        <v>969</v>
+        <v>896</v>
       </c>
       <c r="L50" t="n">
-        <v>888.2</v>
+        <v>883</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>898</v>
+        <v>861</v>
       </c>
       <c r="C51" t="n">
-        <v>901</v>
+        <v>867</v>
       </c>
       <c r="D51" t="n">
-        <v>829</v>
+        <v>893</v>
       </c>
       <c r="E51" t="n">
-        <v>815</v>
+        <v>778</v>
       </c>
       <c r="F51" t="n">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="G51" t="n">
-        <v>884</v>
+        <v>834</v>
       </c>
       <c r="H51" t="n">
-        <v>824</v>
+        <v>947</v>
       </c>
       <c r="I51" t="n">
-        <v>869</v>
+        <v>852</v>
       </c>
       <c r="J51" t="n">
-        <v>886</v>
+        <v>804</v>
       </c>
       <c r="K51" t="n">
-        <v>881</v>
+        <v>855</v>
       </c>
       <c r="L51" t="n">
-        <v>860.6</v>
+        <v>850.3</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>894.84</v>
+        <v>871.8200000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>881.38</v>
+        <v>882.02</v>
       </c>
       <c r="D52" t="n">
-        <v>882.42</v>
+        <v>892.1799999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>895</v>
+        <v>881.9</v>
       </c>
       <c r="F52" t="n">
-        <v>886.16</v>
+        <v>869.62</v>
       </c>
       <c r="G52" t="n">
-        <v>876.14</v>
+        <v>879.38</v>
       </c>
       <c r="H52" t="n">
-        <v>888.8</v>
+        <v>863.9400000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>876.0599999999999</v>
+        <v>877.34</v>
       </c>
       <c r="J52" t="n">
-        <v>881.02</v>
+        <v>891.98</v>
       </c>
       <c r="K52" t="n">
-        <v>877.46</v>
+        <v>882.02</v>
       </c>
       <c r="L52" t="n">
-        <v>883.9279999999999</v>
+        <v>879.22</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.755805969238281</v>
+        <v>7.911411762237549</v>
       </c>
       <c r="C2" t="n">
-        <v>8.118818759918213</v>
+        <v>7.232584953308105</v>
       </c>
       <c r="D2" t="n">
-        <v>8.503820419311523</v>
+        <v>8.580147743225098</v>
       </c>
       <c r="E2" t="n">
-        <v>8.669893741607666</v>
+        <v>8.299903631210327</v>
       </c>
       <c r="F2" t="n">
-        <v>8.569148302078247</v>
+        <v>7.141823768615723</v>
       </c>
       <c r="G2" t="n">
-        <v>8.857129812240601</v>
+        <v>7.909368753433228</v>
       </c>
       <c r="H2" t="n">
-        <v>6.902909517288208</v>
+        <v>7.221634149551392</v>
       </c>
       <c r="I2" t="n">
-        <v>7.859954595565796</v>
+        <v>7.471619367599487</v>
       </c>
       <c r="J2" t="n">
-        <v>8.813560724258423</v>
+        <v>6.96427321434021</v>
       </c>
       <c r="K2" t="n">
-        <v>9.483702182769775</v>
+        <v>7.885876655578613</v>
       </c>
       <c r="L2" t="n">
-        <v>8.353474402427674</v>
+        <v>7.661864399909973</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>8.609061002731323</v>
+        <v>7.761221170425415</v>
       </c>
       <c r="C3" t="n">
-        <v>7.07396388053894</v>
+        <v>7.033076763153076</v>
       </c>
       <c r="D3" t="n">
-        <v>7.664000749588013</v>
+        <v>8.472939252853394</v>
       </c>
       <c r="E3" t="n">
-        <v>8.551692962646484</v>
+        <v>7.250524759292603</v>
       </c>
       <c r="F3" t="n">
-        <v>9.087362289428711</v>
+        <v>7.643535614013672</v>
       </c>
       <c r="G3" t="n">
-        <v>6.82759428024292</v>
+        <v>7.433099508285522</v>
       </c>
       <c r="H3" t="n">
-        <v>8.037539482116699</v>
+        <v>8.131807804107666</v>
       </c>
       <c r="I3" t="n">
-        <v>7.077459335327148</v>
+        <v>7.137837171554565</v>
       </c>
       <c r="J3" t="n">
-        <v>7.132342338562012</v>
+        <v>7.541295051574707</v>
       </c>
       <c r="K3" t="n">
-        <v>7.242544651031494</v>
+        <v>8.495851278305054</v>
       </c>
       <c r="L3" t="n">
-        <v>7.730356097221375</v>
+        <v>7.690118837356567</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.406170129776001</v>
+        <v>8.150725603103638</v>
       </c>
       <c r="C4" t="n">
-        <v>7.708808422088623</v>
+        <v>7.906397104263306</v>
       </c>
       <c r="D4" t="n">
-        <v>7.418701887130737</v>
+        <v>7.441049098968506</v>
       </c>
       <c r="E4" t="n">
-        <v>8.995821475982666</v>
+        <v>7.701869964599609</v>
       </c>
       <c r="F4" t="n">
-        <v>6.936803340911865</v>
+        <v>6.983254432678223</v>
       </c>
       <c r="G4" t="n">
-        <v>8.260504484176636</v>
+        <v>7.167255401611328</v>
       </c>
       <c r="H4" t="n">
-        <v>7.74885892868042</v>
+        <v>8.148270606994629</v>
       </c>
       <c r="I4" t="n">
-        <v>7.356400012969971</v>
+        <v>9.227539539337158</v>
       </c>
       <c r="J4" t="n">
-        <v>8.355783700942993</v>
+        <v>7.244160175323486</v>
       </c>
       <c r="K4" t="n">
-        <v>7.445128202438354</v>
+        <v>7.312467813491821</v>
       </c>
       <c r="L4" t="n">
-        <v>7.763298058509827</v>
+        <v>7.728298974037171</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>6.979363441467285</v>
+        <v>8.244583129882812</v>
       </c>
       <c r="C5" t="n">
-        <v>8.724803447723389</v>
+        <v>7.143937587738037</v>
       </c>
       <c r="D5" t="n">
-        <v>6.93996262550354</v>
+        <v>7.38232684135437</v>
       </c>
       <c r="E5" t="n">
-        <v>7.437700986862183</v>
+        <v>7.168352842330933</v>
       </c>
       <c r="F5" t="n">
-        <v>6.994813680648804</v>
+        <v>7.226217985153198</v>
       </c>
       <c r="G5" t="n">
-        <v>6.913707733154297</v>
+        <v>7.39377498626709</v>
       </c>
       <c r="H5" t="n">
-        <v>8.136844396591187</v>
+        <v>6.578370332717896</v>
       </c>
       <c r="I5" t="n">
-        <v>7.047101974487305</v>
+        <v>7.266583681106567</v>
       </c>
       <c r="J5" t="n">
-        <v>6.67152214050293</v>
+        <v>7.028702259063721</v>
       </c>
       <c r="K5" t="n">
-        <v>6.945815086364746</v>
+        <v>7.392778396606445</v>
       </c>
       <c r="L5" t="n">
-        <v>7.279163551330567</v>
+        <v>7.282562804222107</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>7.310898542404175</v>
+        <v>7.338402509689331</v>
       </c>
       <c r="C6" t="n">
-        <v>8.04748010635376</v>
+        <v>7.752837896347046</v>
       </c>
       <c r="D6" t="n">
-        <v>7.705862998962402</v>
+        <v>7.451630353927612</v>
       </c>
       <c r="E6" t="n">
-        <v>6.642071962356567</v>
+        <v>6.848157405853271</v>
       </c>
       <c r="F6" t="n">
-        <v>6.985231399536133</v>
+        <v>6.966874837875366</v>
       </c>
       <c r="G6" t="n">
-        <v>7.296965599060059</v>
+        <v>7.71741771697998</v>
       </c>
       <c r="H6" t="n">
-        <v>7.768723011016846</v>
+        <v>7.219205617904663</v>
       </c>
       <c r="I6" t="n">
-        <v>7.257049083709717</v>
+        <v>6.865154504776001</v>
       </c>
       <c r="J6" t="n">
-        <v>7.7368483543396</v>
+        <v>7.3558669090271</v>
       </c>
       <c r="K6" t="n">
-        <v>7.647641181945801</v>
+        <v>7.589752197265625</v>
       </c>
       <c r="L6" t="n">
-        <v>7.439877223968506</v>
+        <v>7.310529994964599</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>7.982747316360474</v>
+        <v>7.961312532424927</v>
       </c>
       <c r="C7" t="n">
-        <v>7.650603771209717</v>
+        <v>7.881047964096069</v>
       </c>
       <c r="D7" t="n">
-        <v>8.424588680267334</v>
+        <v>8.112914085388184</v>
       </c>
       <c r="E7" t="n">
-        <v>8.05703330039978</v>
+        <v>8.005204200744629</v>
       </c>
       <c r="F7" t="n">
-        <v>8.071457147598267</v>
+        <v>7.608186721801758</v>
       </c>
       <c r="G7" t="n">
-        <v>7.793227434158325</v>
+        <v>8.679924964904785</v>
       </c>
       <c r="H7" t="n">
-        <v>8.503214836120605</v>
+        <v>7.478554010391235</v>
       </c>
       <c r="I7" t="n">
-        <v>8.508394479751587</v>
+        <v>7.793726921081543</v>
       </c>
       <c r="J7" t="n">
-        <v>7.667136430740356</v>
+        <v>7.602239608764648</v>
       </c>
       <c r="K7" t="n">
-        <v>8.526408195495605</v>
+        <v>7.261590957641602</v>
       </c>
       <c r="L7" t="n">
-        <v>8.118481159210205</v>
+        <v>7.838470196723938</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>9.898815393447876</v>
+        <v>7.426689386367798</v>
       </c>
       <c r="C8" t="n">
-        <v>8.204750537872314</v>
+        <v>7.644093036651611</v>
       </c>
       <c r="D8" t="n">
-        <v>8.097472667694092</v>
+        <v>7.600218296051025</v>
       </c>
       <c r="E8" t="n">
-        <v>7.635212182998657</v>
+        <v>8.121360063552856</v>
       </c>
       <c r="F8" t="n">
-        <v>7.897016286849976</v>
+        <v>7.031727313995361</v>
       </c>
       <c r="G8" t="n">
-        <v>7.588779926300049</v>
+        <v>7.504978895187378</v>
       </c>
       <c r="H8" t="n">
-        <v>7.359876394271851</v>
+        <v>7.932862281799316</v>
       </c>
       <c r="I8" t="n">
-        <v>8.301447629928589</v>
+        <v>7.494001865386963</v>
       </c>
       <c r="J8" t="n">
-        <v>7.845139741897583</v>
+        <v>7.532927513122559</v>
       </c>
       <c r="K8" t="n">
-        <v>8.295203685760498</v>
+        <v>8.115424394607544</v>
       </c>
       <c r="L8" t="n">
-        <v>8.112371444702148</v>
+        <v>7.640428304672241</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>7.758391380310059</v>
+        <v>7.470051050186157</v>
       </c>
       <c r="C9" t="n">
-        <v>8.14480447769165</v>
+        <v>7.578763723373413</v>
       </c>
       <c r="D9" t="n">
-        <v>8.09200382232666</v>
+        <v>8.422146558761597</v>
       </c>
       <c r="E9" t="n">
-        <v>9.583116769790649</v>
+        <v>7.456106662750244</v>
       </c>
       <c r="F9" t="n">
-        <v>8.767861604690552</v>
+        <v>7.830700397491455</v>
       </c>
       <c r="G9" t="n">
-        <v>7.528547286987305</v>
+        <v>8.16428017616272</v>
       </c>
       <c r="H9" t="n">
-        <v>8.54981517791748</v>
+        <v>7.20627498626709</v>
       </c>
       <c r="I9" t="n">
-        <v>8.454012155532837</v>
+        <v>6.993788242340088</v>
       </c>
       <c r="J9" t="n">
-        <v>8.334501266479492</v>
+        <v>8.058117151260376</v>
       </c>
       <c r="K9" t="n">
-        <v>7.918929100036621</v>
+        <v>7.370809078216553</v>
       </c>
       <c r="L9" t="n">
-        <v>8.31319830417633</v>
+        <v>7.655103802680969</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>7.608204126358032</v>
+        <v>7.228193998336792</v>
       </c>
       <c r="C10" t="n">
-        <v>7.311541557312012</v>
+        <v>6.883728265762329</v>
       </c>
       <c r="D10" t="n">
-        <v>7.34641432762146</v>
+        <v>6.718822240829468</v>
       </c>
       <c r="E10" t="n">
-        <v>9.635950565338135</v>
+        <v>7.037089824676514</v>
       </c>
       <c r="F10" t="n">
-        <v>8.049088954925537</v>
+        <v>6.589207887649536</v>
       </c>
       <c r="G10" t="n">
-        <v>6.401396036148071</v>
+        <v>6.770251035690308</v>
       </c>
       <c r="H10" t="n">
-        <v>6.652204275131226</v>
+        <v>7.16478157043457</v>
       </c>
       <c r="I10" t="n">
-        <v>6.336062669754028</v>
+        <v>6.407661914825439</v>
       </c>
       <c r="J10" t="n">
-        <v>7.577804565429688</v>
+        <v>6.801677465438843</v>
       </c>
       <c r="K10" t="n">
-        <v>6.726022958755493</v>
+        <v>7.5700523853302</v>
       </c>
       <c r="L10" t="n">
-        <v>7.364469003677368</v>
+        <v>6.9171466588974</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>6.449230909347534</v>
+        <v>6.804330348968506</v>
       </c>
       <c r="C11" t="n">
-        <v>6.44325590133667</v>
+        <v>6.889635562896729</v>
       </c>
       <c r="D11" t="n">
-        <v>6.16998291015625</v>
+        <v>6.257728815078735</v>
       </c>
       <c r="E11" t="n">
-        <v>7.295536518096924</v>
+        <v>7.071111440658569</v>
       </c>
       <c r="F11" t="n">
-        <v>6.708487272262573</v>
+        <v>6.862153291702271</v>
       </c>
       <c r="G11" t="n">
-        <v>7.112884998321533</v>
+        <v>6.550957202911377</v>
       </c>
       <c r="H11" t="n">
-        <v>6.499951124191284</v>
+        <v>7.052648305892944</v>
       </c>
       <c r="I11" t="n">
-        <v>7.459497690200806</v>
+        <v>6.370434522628784</v>
       </c>
       <c r="J11" t="n">
-        <v>7.026134729385376</v>
+        <v>6.374925136566162</v>
       </c>
       <c r="K11" t="n">
-        <v>6.620284795761108</v>
+        <v>6.564967393875122</v>
       </c>
       <c r="L11" t="n">
-        <v>6.778524684906006</v>
+        <v>6.67988920211792</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>7.52892541885376</v>
+        <v>6.793354272842407</v>
       </c>
       <c r="C12" t="n">
-        <v>6.858655214309692</v>
+        <v>7.255162239074707</v>
       </c>
       <c r="D12" t="n">
-        <v>6.980333805084229</v>
+        <v>7.026706218719482</v>
       </c>
       <c r="E12" t="n">
-        <v>6.433257579803467</v>
+        <v>7.339420080184937</v>
       </c>
       <c r="F12" t="n">
-        <v>7.196277618408203</v>
+        <v>7.581294536590576</v>
       </c>
       <c r="G12" t="n">
-        <v>7.112979173660278</v>
+        <v>8.086488723754883</v>
       </c>
       <c r="H12" t="n">
-        <v>6.688083648681641</v>
+        <v>6.695068836212158</v>
       </c>
       <c r="I12" t="n">
-        <v>7.077684879302979</v>
+        <v>7.196811199188232</v>
       </c>
       <c r="J12" t="n">
-        <v>7.058638334274292</v>
+        <v>8.026688575744629</v>
       </c>
       <c r="K12" t="n">
-        <v>6.728001356124878</v>
+        <v>7.23405909538269</v>
       </c>
       <c r="L12" t="n">
-        <v>6.966283702850342</v>
+        <v>7.32350537776947</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.349382400512695</v>
+        <v>8.043554782867432</v>
       </c>
       <c r="C13" t="n">
-        <v>8.657983541488647</v>
+        <v>7.241583824157715</v>
       </c>
       <c r="D13" t="n">
-        <v>7.118996858596802</v>
+        <v>6.834610462188721</v>
       </c>
       <c r="E13" t="n">
-        <v>8.256524801254272</v>
+        <v>7.327824354171753</v>
       </c>
       <c r="F13" t="n">
-        <v>7.007811069488525</v>
+        <v>6.305943012237549</v>
       </c>
       <c r="G13" t="n">
-        <v>6.933480739593506</v>
+        <v>6.618176937103271</v>
       </c>
       <c r="H13" t="n">
-        <v>6.742479562759399</v>
+        <v>7.822106599807739</v>
       </c>
       <c r="I13" t="n">
-        <v>6.72299861907959</v>
+        <v>6.954301595687866</v>
       </c>
       <c r="J13" t="n">
-        <v>6.846245527267456</v>
+        <v>8.571673631668091</v>
       </c>
       <c r="K13" t="n">
-        <v>6.754948139190674</v>
+        <v>6.899649143218994</v>
       </c>
       <c r="L13" t="n">
-        <v>7.239085125923157</v>
+        <v>7.261942434310913</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>8.83100962638855</v>
+        <v>7.664998054504395</v>
       </c>
       <c r="C14" t="n">
-        <v>7.344389200210571</v>
+        <v>9.169356822967529</v>
       </c>
       <c r="D14" t="n">
-        <v>7.733379364013672</v>
+        <v>9.916714906692505</v>
       </c>
       <c r="E14" t="n">
-        <v>9.511737108230591</v>
+        <v>7.757912635803223</v>
       </c>
       <c r="F14" t="n">
-        <v>7.35278844833374</v>
+        <v>8.567159414291382</v>
       </c>
       <c r="G14" t="n">
-        <v>7.627584218978882</v>
+        <v>7.792143106460571</v>
       </c>
       <c r="H14" t="n">
-        <v>7.718849420547485</v>
+        <v>8.113834381103516</v>
       </c>
       <c r="I14" t="n">
-        <v>7.684954643249512</v>
+        <v>7.144310712814331</v>
       </c>
       <c r="J14" t="n">
-        <v>7.718855619430542</v>
+        <v>7.944257974624634</v>
       </c>
       <c r="K14" t="n">
-        <v>7.351779460906982</v>
+        <v>7.601650238037109</v>
       </c>
       <c r="L14" t="n">
-        <v>7.887532711029053</v>
+        <v>8.167233824729919</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>7.704352378845215</v>
+        <v>8.159694910049438</v>
       </c>
       <c r="C15" t="n">
-        <v>9.09036922454834</v>
+        <v>7.85849666595459</v>
       </c>
       <c r="D15" t="n">
-        <v>9.086398363113403</v>
+        <v>7.827086210250854</v>
       </c>
       <c r="E15" t="n">
-        <v>7.892875909805298</v>
+        <v>9.147219181060791</v>
       </c>
       <c r="F15" t="n">
-        <v>7.315842628479004</v>
+        <v>8.219050168991089</v>
       </c>
       <c r="G15" t="n">
-        <v>8.257524490356445</v>
+        <v>7.891417503356934</v>
       </c>
       <c r="H15" t="n">
-        <v>7.987181901931763</v>
+        <v>8.034525156021118</v>
       </c>
       <c r="I15" t="n">
-        <v>8.144241571426392</v>
+        <v>7.291939258575439</v>
       </c>
       <c r="J15" t="n">
-        <v>8.542749881744385</v>
+        <v>8.407608985900879</v>
       </c>
       <c r="K15" t="n">
-        <v>7.862948894500732</v>
+        <v>9.674355506896973</v>
       </c>
       <c r="L15" t="n">
-        <v>8.188448524475097</v>
+        <v>8.25113935470581</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.249529838562012</v>
+        <v>7.094435691833496</v>
       </c>
       <c r="C16" t="n">
-        <v>6.858513832092285</v>
+        <v>6.599210500717163</v>
       </c>
       <c r="D16" t="n">
-        <v>7.888398408889771</v>
+        <v>7.218603849411011</v>
       </c>
       <c r="E16" t="n">
-        <v>7.692935705184937</v>
+        <v>8.055458307266235</v>
       </c>
       <c r="F16" t="n">
-        <v>6.893420696258545</v>
+        <v>6.981457948684692</v>
       </c>
       <c r="G16" t="n">
-        <v>6.862040996551514</v>
+        <v>7.057653903961182</v>
       </c>
       <c r="H16" t="n">
-        <v>7.097428321838379</v>
+        <v>6.820281982421875</v>
       </c>
       <c r="I16" t="n">
-        <v>7.714890241622925</v>
+        <v>7.153404474258423</v>
       </c>
       <c r="J16" t="n">
-        <v>6.749378204345703</v>
+        <v>6.707072496414185</v>
       </c>
       <c r="K16" t="n">
-        <v>6.722359895706177</v>
+        <v>7.057622194290161</v>
       </c>
       <c r="L16" t="n">
-        <v>7.172889614105225</v>
+        <v>7.074520134925843</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>9.157210350036621</v>
+        <v>7.180305957794189</v>
       </c>
       <c r="C17" t="n">
-        <v>7.781180620193481</v>
+        <v>7.286556720733643</v>
       </c>
       <c r="D17" t="n">
-        <v>7.614602327346802</v>
+        <v>7.477013349533081</v>
       </c>
       <c r="E17" t="n">
-        <v>8.142747640609741</v>
+        <v>7.771795272827148</v>
       </c>
       <c r="F17" t="n">
-        <v>7.50368070602417</v>
+        <v>9.711741924285889</v>
       </c>
       <c r="G17" t="n">
-        <v>7.570735692977905</v>
+        <v>8.112836837768555</v>
       </c>
       <c r="H17" t="n">
-        <v>7.675427198410034</v>
+        <v>7.190163612365723</v>
       </c>
       <c r="I17" t="n">
-        <v>7.105403184890747</v>
+        <v>7.877448320388794</v>
       </c>
       <c r="J17" t="n">
-        <v>7.341161489486694</v>
+        <v>8.113843679428101</v>
       </c>
       <c r="K17" t="n">
-        <v>7.545425653457642</v>
+        <v>7.305883884429932</v>
       </c>
       <c r="L17" t="n">
-        <v>7.743757486343384</v>
+        <v>7.802758955955506</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>7.890473127365112</v>
+        <v>8.639962911605835</v>
       </c>
       <c r="C18" t="n">
-        <v>7.687501192092896</v>
+        <v>8.305347442626953</v>
       </c>
       <c r="D18" t="n">
-        <v>8.250547409057617</v>
+        <v>9.03397536277771</v>
       </c>
       <c r="E18" t="n">
-        <v>8.724816560745239</v>
+        <v>7.766711950302124</v>
       </c>
       <c r="F18" t="n">
-        <v>8.15079140663147</v>
+        <v>8.23600959777832</v>
       </c>
       <c r="G18" t="n">
-        <v>8.241566896438599</v>
+        <v>9.132781028747559</v>
       </c>
       <c r="H18" t="n">
-        <v>8.897358179092407</v>
+        <v>7.853963136672974</v>
       </c>
       <c r="I18" t="n">
-        <v>8.834003925323486</v>
+        <v>9.045960426330566</v>
       </c>
       <c r="J18" t="n">
-        <v>8.631531000137329</v>
+        <v>7.816084861755371</v>
       </c>
       <c r="K18" t="n">
-        <v>7.910957813262939</v>
+        <v>8.84447717666626</v>
       </c>
       <c r="L18" t="n">
-        <v>8.32195475101471</v>
+        <v>8.467527389526367</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>5.976478338241577</v>
+        <v>6.437105894088745</v>
       </c>
       <c r="C19" t="n">
-        <v>6.260570287704468</v>
+        <v>6.291979551315308</v>
       </c>
       <c r="D19" t="n">
-        <v>5.996762037277222</v>
+        <v>6.969366550445557</v>
       </c>
       <c r="E19" t="n">
-        <v>7.854026556015015</v>
+        <v>6.490633249282837</v>
       </c>
       <c r="F19" t="n">
-        <v>7.06102991104126</v>
+        <v>6.460202932357788</v>
       </c>
       <c r="G19" t="n">
-        <v>6.515899896621704</v>
+        <v>6.025331020355225</v>
       </c>
       <c r="H19" t="n">
-        <v>8.435525894165039</v>
+        <v>6.909509897232056</v>
       </c>
       <c r="I19" t="n">
-        <v>7.003186702728271</v>
+        <v>7.257602691650391</v>
       </c>
       <c r="J19" t="n">
-        <v>7.509195804595947</v>
+        <v>6.566432237625122</v>
       </c>
       <c r="K19" t="n">
-        <v>6.267203330993652</v>
+        <v>6.99481463432312</v>
       </c>
       <c r="L19" t="n">
-        <v>6.887987875938416</v>
+        <v>6.640297865867614</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>8.580192804336548</v>
+        <v>6.984825849533081</v>
       </c>
       <c r="C20" t="n">
-        <v>7.086053609848022</v>
+        <v>6.799296617507935</v>
       </c>
       <c r="D20" t="n">
-        <v>7.223755359649658</v>
+        <v>7.214230060577393</v>
       </c>
       <c r="E20" t="n">
-        <v>7.833040714263916</v>
+        <v>7.157870054244995</v>
       </c>
       <c r="F20" t="n">
-        <v>6.835103750228882</v>
+        <v>6.660661458969116</v>
       </c>
       <c r="G20" t="n">
-        <v>6.901396989822388</v>
+        <v>7.112004041671753</v>
       </c>
       <c r="H20" t="n">
-        <v>7.706872940063477</v>
+        <v>7.186334609985352</v>
       </c>
       <c r="I20" t="n">
-        <v>7.932311058044434</v>
+        <v>7.588480472564697</v>
       </c>
       <c r="J20" t="n">
-        <v>7.190693616867065</v>
+        <v>7.25051736831665</v>
       </c>
       <c r="K20" t="n">
-        <v>7.041077375411987</v>
+        <v>7.199681282043457</v>
       </c>
       <c r="L20" t="n">
-        <v>7.433049821853638</v>
+        <v>7.115390181541443</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>7.498927593231201</v>
+        <v>7.237548828125</v>
       </c>
       <c r="C21" t="n">
-        <v>8.177231788635254</v>
+        <v>7.447515249252319</v>
       </c>
       <c r="D21" t="n">
-        <v>7.688004970550537</v>
+        <v>8.181653261184692</v>
       </c>
       <c r="E21" t="n">
-        <v>7.309441566467285</v>
+        <v>7.38517951965332</v>
       </c>
       <c r="F21" t="n">
-        <v>8.635567903518677</v>
+        <v>8.953683137893677</v>
       </c>
       <c r="G21" t="n">
-        <v>7.52835488319397</v>
+        <v>8.302348375320435</v>
       </c>
       <c r="H21" t="n">
-        <v>7.957237958908081</v>
+        <v>6.337356805801392</v>
       </c>
       <c r="I21" t="n">
-        <v>7.404131650924683</v>
+        <v>6.89495062828064</v>
       </c>
       <c r="J21" t="n">
-        <v>7.118357181549072</v>
+        <v>8.407580852508545</v>
       </c>
       <c r="K21" t="n">
-        <v>7.136352062225342</v>
+        <v>6.988189220428467</v>
       </c>
       <c r="L21" t="n">
-        <v>7.64536075592041</v>
+        <v>7.613600587844848</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>7.6235671043396</v>
+        <v>7.10141658782959</v>
       </c>
       <c r="C22" t="n">
-        <v>6.485141515731812</v>
+        <v>7.065958738327026</v>
       </c>
       <c r="D22" t="n">
-        <v>8.926777362823486</v>
+        <v>7.103510618209839</v>
       </c>
       <c r="E22" t="n">
-        <v>6.789754390716553</v>
+        <v>8.558226585388184</v>
       </c>
       <c r="F22" t="n">
-        <v>7.210639476776123</v>
+        <v>7.996108531951904</v>
       </c>
       <c r="G22" t="n">
-        <v>8.174701690673828</v>
+        <v>7.238047122955322</v>
       </c>
       <c r="H22" t="n">
-        <v>8.007601976394653</v>
+        <v>7.66845440864563</v>
       </c>
       <c r="I22" t="n">
-        <v>8.373669385910034</v>
+        <v>7.482446432113647</v>
       </c>
       <c r="J22" t="n">
-        <v>7.551231384277344</v>
+        <v>8.04654860496521</v>
       </c>
       <c r="K22" t="n">
-        <v>6.936871528625488</v>
+        <v>12.93486142158508</v>
       </c>
       <c r="L22" t="n">
-        <v>7.607995581626892</v>
+        <v>8.119557905197144</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>8.106871128082275</v>
+        <v>7.970713138580322</v>
       </c>
       <c r="C23" t="n">
-        <v>9.605073928833008</v>
+        <v>8.605104446411133</v>
       </c>
       <c r="D23" t="n">
-        <v>8.511823177337646</v>
+        <v>10.22593998908997</v>
       </c>
       <c r="E23" t="n">
-        <v>7.704875469207764</v>
+        <v>7.964186906814575</v>
       </c>
       <c r="F23" t="n">
-        <v>7.307888984680176</v>
+        <v>8.521763801574707</v>
       </c>
       <c r="G23" t="n">
-        <v>7.510356426239014</v>
+        <v>8.199090003967285</v>
       </c>
       <c r="H23" t="n">
-        <v>7.513358116149902</v>
+        <v>8.457463264465332</v>
       </c>
       <c r="I23" t="n">
-        <v>8.193121433258057</v>
+        <v>9.401068449020386</v>
       </c>
       <c r="J23" t="n">
-        <v>8.274931669235229</v>
+        <v>9.431003332138062</v>
       </c>
       <c r="K23" t="n">
-        <v>7.555762767791748</v>
+        <v>7.627168893814087</v>
       </c>
       <c r="L23" t="n">
-        <v>8.028406310081483</v>
+        <v>8.640350222587585</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>6.325390338897705</v>
+        <v>8.279455423355103</v>
       </c>
       <c r="C24" t="n">
-        <v>8.218069553375244</v>
+        <v>8.227891206741333</v>
       </c>
       <c r="D24" t="n">
-        <v>6.530866146087646</v>
+        <v>6.603193044662476</v>
       </c>
       <c r="E24" t="n">
-        <v>6.806658744812012</v>
+        <v>6.932853698730469</v>
       </c>
       <c r="F24" t="n">
-        <v>7.34278416633606</v>
+        <v>8.012654542922974</v>
       </c>
       <c r="G24" t="n">
-        <v>6.911929607391357</v>
+        <v>8.036519765853882</v>
       </c>
       <c r="H24" t="n">
-        <v>6.652044773101807</v>
+        <v>7.050535678863525</v>
       </c>
       <c r="I24" t="n">
-        <v>6.820623874664307</v>
+        <v>6.699431657791138</v>
       </c>
       <c r="J24" t="n">
-        <v>7.332803010940552</v>
+        <v>6.700930595397949</v>
       </c>
       <c r="K24" t="n">
-        <v>8.270428657531738</v>
+        <v>7.106413125991821</v>
       </c>
       <c r="L24" t="n">
-        <v>7.121159887313842</v>
+        <v>7.364987874031067</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>9.60850191116333</v>
+        <v>10.78851199150085</v>
       </c>
       <c r="C25" t="n">
-        <v>8.159700870513916</v>
+        <v>8.762187004089355</v>
       </c>
       <c r="D25" t="n">
-        <v>9.344216823577881</v>
+        <v>9.310815095901489</v>
       </c>
       <c r="E25" t="n">
-        <v>9.511735439300537</v>
+        <v>9.320742845535278</v>
       </c>
       <c r="F25" t="n">
-        <v>8.03404712677002</v>
+        <v>8.694336175918579</v>
       </c>
       <c r="G25" t="n">
-        <v>7.772681474685669</v>
+        <v>8.835484504699707</v>
       </c>
       <c r="H25" t="n">
-        <v>8.122791767120361</v>
+        <v>7.611602544784546</v>
       </c>
       <c r="I25" t="n">
-        <v>9.261920213699341</v>
+        <v>8.092863082885742</v>
       </c>
       <c r="J25" t="n">
-        <v>9.602035045623779</v>
+        <v>8.280430555343628</v>
       </c>
       <c r="K25" t="n">
-        <v>8.460993051528931</v>
+        <v>9.939164638519287</v>
       </c>
       <c r="L25" t="n">
-        <v>8.787862372398376</v>
+        <v>8.963613843917846</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>8.251960515975952</v>
+        <v>7.894400358200073</v>
       </c>
       <c r="C26" t="n">
-        <v>7.603641510009766</v>
+        <v>8.580631017684937</v>
       </c>
       <c r="D26" t="n">
-        <v>7.895382404327393</v>
+        <v>7.983671903610229</v>
       </c>
       <c r="E26" t="n">
-        <v>8.528775930404663</v>
+        <v>8.272409915924072</v>
       </c>
       <c r="F26" t="n">
-        <v>8.328540563583374</v>
+        <v>7.342772722244263</v>
       </c>
       <c r="G26" t="n">
-        <v>8.551724910736084</v>
+        <v>7.682467460632324</v>
       </c>
       <c r="H26" t="n">
-        <v>7.547774314880371</v>
+        <v>8.184149026870728</v>
       </c>
       <c r="I26" t="n">
-        <v>7.980165243148804</v>
+        <v>7.250529289245605</v>
       </c>
       <c r="J26" t="n">
-        <v>8.15924596786499</v>
+        <v>8.556237936019897</v>
       </c>
       <c r="K26" t="n">
-        <v>8.516788959503174</v>
+        <v>7.396144151687622</v>
       </c>
       <c r="L26" t="n">
-        <v>8.136400032043458</v>
+        <v>7.914341378211975</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>7.781681060791016</v>
+        <v>9.028021335601807</v>
       </c>
       <c r="C27" t="n">
-        <v>8.216086149215698</v>
+        <v>8.418553113937378</v>
       </c>
       <c r="D27" t="n">
-        <v>8.696320056915283</v>
+        <v>8.023579359054565</v>
       </c>
       <c r="E27" t="n">
-        <v>8.055468797683716</v>
+        <v>10.39650845527649</v>
       </c>
       <c r="F27" t="n">
-        <v>8.871423482894897</v>
+        <v>8.636000156402588</v>
       </c>
       <c r="G27" t="n">
-        <v>8.571819067001343</v>
+        <v>9.082823276519775</v>
       </c>
       <c r="H27" t="n">
-        <v>8.414119482040405</v>
+        <v>8.637007713317871</v>
       </c>
       <c r="I27" t="n">
-        <v>9.899183750152588</v>
+        <v>9.2135329246521</v>
       </c>
       <c r="J27" t="n">
-        <v>8.583663940429688</v>
+        <v>9.246917963027954</v>
       </c>
       <c r="K27" t="n">
-        <v>8.816078662872314</v>
+        <v>7.906683683395386</v>
       </c>
       <c r="L27" t="n">
-        <v>8.590584444999696</v>
+        <v>8.858962798118592</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.024742126464844</v>
+        <v>7.450640678405762</v>
       </c>
       <c r="C28" t="n">
-        <v>7.047165870666504</v>
+        <v>6.769773960113525</v>
       </c>
       <c r="D28" t="n">
-        <v>7.015776634216309</v>
+        <v>6.971731424331665</v>
       </c>
       <c r="E28" t="n">
-        <v>6.945453405380249</v>
+        <v>7.08744215965271</v>
       </c>
       <c r="F28" t="n">
-        <v>6.823259115219116</v>
+        <v>7.314876794815063</v>
       </c>
       <c r="G28" t="n">
-        <v>7.029735803604126</v>
+        <v>8.523416757583618</v>
       </c>
       <c r="H28" t="n">
-        <v>7.109041929244995</v>
+        <v>7.325850486755371</v>
       </c>
       <c r="I28" t="n">
-        <v>6.632683515548706</v>
+        <v>6.828614950180054</v>
       </c>
       <c r="J28" t="n">
-        <v>6.583713293075562</v>
+        <v>7.692922115325928</v>
       </c>
       <c r="K28" t="n">
-        <v>6.788698434829712</v>
+        <v>6.84557318687439</v>
       </c>
       <c r="L28" t="n">
-        <v>6.900027012825012</v>
+        <v>7.281084251403809</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.290966033935547</v>
+        <v>6.841562747955322</v>
       </c>
       <c r="C29" t="n">
-        <v>7.708879709243774</v>
+        <v>7.251036643981934</v>
       </c>
       <c r="D29" t="n">
-        <v>7.443128347396851</v>
+        <v>8.617052316665649</v>
       </c>
       <c r="E29" t="n">
-        <v>7.377216577529907</v>
+        <v>8.085418939590454</v>
       </c>
       <c r="F29" t="n">
-        <v>7.193188428878784</v>
+        <v>7.394178867340088</v>
       </c>
       <c r="G29" t="n">
-        <v>7.447530746459961</v>
+        <v>6.672524929046631</v>
       </c>
       <c r="H29" t="n">
-        <v>7.588165998458862</v>
+        <v>7.356429100036621</v>
       </c>
       <c r="I29" t="n">
-        <v>7.540874242782593</v>
+        <v>7.727789402008057</v>
       </c>
       <c r="J29" t="n">
-        <v>7.505000352859497</v>
+        <v>7.058542490005493</v>
       </c>
       <c r="K29" t="n">
-        <v>7.196277856826782</v>
+        <v>6.926824331283569</v>
       </c>
       <c r="L29" t="n">
-        <v>7.429122829437256</v>
+        <v>7.393135976791382</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>8.529321193695068</v>
+        <v>7.048019886016846</v>
       </c>
       <c r="C30" t="n">
-        <v>7.435655832290649</v>
+        <v>7.381306648254395</v>
       </c>
       <c r="D30" t="n">
-        <v>6.497608661651611</v>
+        <v>7.310469627380371</v>
       </c>
       <c r="E30" t="n">
-        <v>7.708444118499756</v>
+        <v>7.347407579421997</v>
       </c>
       <c r="F30" t="n">
-        <v>7.328438758850098</v>
+        <v>7.164367914199829</v>
       </c>
       <c r="G30" t="n">
-        <v>7.632238864898682</v>
+        <v>7.170854091644287</v>
       </c>
       <c r="H30" t="n">
-        <v>7.599234580993652</v>
+        <v>6.931814670562744</v>
       </c>
       <c r="I30" t="n">
-        <v>7.489819288253784</v>
+        <v>7.33680272102356</v>
       </c>
       <c r="J30" t="n">
-        <v>6.997666597366333</v>
+        <v>7.084489345550537</v>
       </c>
       <c r="K30" t="n">
-        <v>7.211642265319824</v>
+        <v>6.523877143859863</v>
       </c>
       <c r="L30" t="n">
-        <v>7.443007016181946</v>
+        <v>7.129940962791443</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.042034149169922</v>
+        <v>8.361758947372437</v>
       </c>
       <c r="C31" t="n">
-        <v>8.392120122909546</v>
+        <v>7.363762378692627</v>
       </c>
       <c r="D31" t="n">
-        <v>8.36369514465332</v>
+        <v>8.881919860839844</v>
       </c>
       <c r="E31" t="n">
-        <v>8.108825922012329</v>
+        <v>6.878466367721558</v>
       </c>
       <c r="F31" t="n">
-        <v>9.040612936019897</v>
+        <v>7.280427932739258</v>
       </c>
       <c r="G31" t="n">
-        <v>9.019038915634155</v>
+        <v>6.956296682357788</v>
       </c>
       <c r="H31" t="n">
-        <v>8.321346044540405</v>
+        <v>6.9298415184021</v>
       </c>
       <c r="I31" t="n">
-        <v>6.969738006591797</v>
+        <v>7.025123596191406</v>
       </c>
       <c r="J31" t="n">
-        <v>7.929799795150757</v>
+        <v>7.926321506500244</v>
       </c>
       <c r="K31" t="n">
-        <v>8.374168634414673</v>
+        <v>7.351743936538696</v>
       </c>
       <c r="L31" t="n">
-        <v>8.25613796710968</v>
+        <v>7.495566272735596</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>8.363718748092651</v>
+        <v>8.28043007850647</v>
       </c>
       <c r="C32" t="n">
-        <v>8.543739795684814</v>
+        <v>7.816120624542236</v>
       </c>
       <c r="D32" t="n">
-        <v>9.021037340164185</v>
+        <v>10.12871360778809</v>
       </c>
       <c r="E32" t="n">
-        <v>8.807560682296753</v>
+        <v>9.207564353942871</v>
       </c>
       <c r="F32" t="n">
-        <v>10.79701638221741</v>
+        <v>9.840908288955688</v>
       </c>
       <c r="G32" t="n">
-        <v>7.879424571990967</v>
+        <v>8.054477691650391</v>
       </c>
       <c r="H32" t="n">
-        <v>8.410581350326538</v>
+        <v>9.308788299560547</v>
       </c>
       <c r="I32" t="n">
-        <v>9.631522655487061</v>
+        <v>8.338303565979004</v>
       </c>
       <c r="J32" t="n">
-        <v>7.574750185012817</v>
+        <v>9.82232666015625</v>
       </c>
       <c r="K32" t="n">
-        <v>7.98019552230835</v>
+        <v>7.845093011856079</v>
       </c>
       <c r="L32" t="n">
-        <v>8.700954723358155</v>
+        <v>8.864272618293763</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>6.903909206390381</v>
+        <v>8.210641384124756</v>
       </c>
       <c r="C33" t="n">
-        <v>8.485869169235229</v>
+        <v>7.501978874206543</v>
       </c>
       <c r="D33" t="n">
-        <v>7.270462274551392</v>
+        <v>7.13093376159668</v>
       </c>
       <c r="E33" t="n">
-        <v>7.046586990356445</v>
+        <v>7.131922006607056</v>
       </c>
       <c r="F33" t="n">
-        <v>9.00255274772644</v>
+        <v>8.4170823097229</v>
       </c>
       <c r="G33" t="n">
-        <v>7.193705320358276</v>
+        <v>7.57282567024231</v>
       </c>
       <c r="H33" t="n">
-        <v>7.522336721420288</v>
+        <v>8.937730550765991</v>
       </c>
       <c r="I33" t="n">
-        <v>6.912892580032349</v>
+        <v>7.421687126159668</v>
       </c>
       <c r="J33" t="n">
-        <v>7.100406646728516</v>
+        <v>7.927882671356201</v>
       </c>
       <c r="K33" t="n">
-        <v>6.916870832443237</v>
+        <v>8.845098972320557</v>
       </c>
       <c r="L33" t="n">
-        <v>7.435559248924255</v>
+        <v>7.909778332710266</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>7.852485179901123</v>
+        <v>7.568311929702759</v>
       </c>
       <c r="C34" t="n">
-        <v>7.692386627197266</v>
+        <v>7.406726121902466</v>
       </c>
       <c r="D34" t="n">
-        <v>7.345303058624268</v>
+        <v>7.944841146469116</v>
       </c>
       <c r="E34" t="n">
-        <v>8.247990369796753</v>
+        <v>7.51704216003418</v>
       </c>
       <c r="F34" t="n">
-        <v>7.399146556854248</v>
+        <v>9.002628087997437</v>
       </c>
       <c r="G34" t="n">
-        <v>7.395657062530518</v>
+        <v>7.813719987869263</v>
       </c>
       <c r="H34" t="n">
-        <v>7.707893848419189</v>
+        <v>7.084559917449951</v>
       </c>
       <c r="I34" t="n">
-        <v>7.783202171325684</v>
+        <v>7.567336320877075</v>
       </c>
       <c r="J34" t="n">
-        <v>7.887387037277222</v>
+        <v>8.289422988891602</v>
       </c>
       <c r="K34" t="n">
-        <v>9.146216154098511</v>
+        <v>7.890962600708008</v>
       </c>
       <c r="L34" t="n">
-        <v>7.845766806602478</v>
+        <v>7.808555126190186</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.21362566947937</v>
+        <v>8.807092666625977</v>
       </c>
       <c r="C35" t="n">
-        <v>8.652949094772339</v>
+        <v>7.063117265701294</v>
       </c>
       <c r="D35" t="n">
-        <v>7.509322643280029</v>
+        <v>7.634170770645142</v>
       </c>
       <c r="E35" t="n">
-        <v>8.215622901916504</v>
+        <v>7.233168601989746</v>
       </c>
       <c r="F35" t="n">
-        <v>7.858110666275024</v>
+        <v>7.196290016174316</v>
       </c>
       <c r="G35" t="n">
-        <v>7.324439287185669</v>
+        <v>6.780858516693115</v>
       </c>
       <c r="H35" t="n">
-        <v>8.464002847671509</v>
+        <v>7.660580158233643</v>
       </c>
       <c r="I35" t="n">
-        <v>7.017752647399902</v>
+        <v>8.375713109970093</v>
       </c>
       <c r="J35" t="n">
-        <v>7.044665813446045</v>
+        <v>7.577615737915039</v>
       </c>
       <c r="K35" t="n">
-        <v>7.375947237014771</v>
+        <v>7.432037115097046</v>
       </c>
       <c r="L35" t="n">
-        <v>7.667643880844116</v>
+        <v>7.576064395904541</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>7.750333786010742</v>
+        <v>8.887847661972046</v>
       </c>
       <c r="C36" t="n">
-        <v>8.759212970733643</v>
+        <v>7.293900728225708</v>
       </c>
       <c r="D36" t="n">
-        <v>8.235656023025513</v>
+        <v>7.600631475448608</v>
       </c>
       <c r="E36" t="n">
-        <v>7.190304040908813</v>
+        <v>7.479919910430908</v>
       </c>
       <c r="F36" t="n">
-        <v>8.581215381622314</v>
+        <v>7.896400690078735</v>
       </c>
       <c r="G36" t="n">
-        <v>7.422700881958008</v>
+        <v>7.709901332855225</v>
       </c>
       <c r="H36" t="n">
-        <v>7.523934125900269</v>
+        <v>8.982119083404541</v>
       </c>
       <c r="I36" t="n">
-        <v>7.142428874969482</v>
+        <v>8.014596462249756</v>
       </c>
       <c r="J36" t="n">
-        <v>6.596354484558105</v>
+        <v>7.331872940063477</v>
       </c>
       <c r="K36" t="n">
-        <v>7.93336820602417</v>
+        <v>8.076414108276367</v>
       </c>
       <c r="L36" t="n">
-        <v>7.713550877571106</v>
+        <v>7.927360439300537</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>7.322469711303711</v>
+        <v>7.143303632736206</v>
       </c>
       <c r="C37" t="n">
-        <v>6.751935958862305</v>
+        <v>7.981128215789795</v>
       </c>
       <c r="D37" t="n">
-        <v>8.305978775024414</v>
+        <v>7.392783641815186</v>
       </c>
       <c r="E37" t="n">
-        <v>10.78017807006836</v>
+        <v>7.244174480438232</v>
       </c>
       <c r="F37" t="n">
-        <v>7.296020030975342</v>
+        <v>6.725979566574097</v>
       </c>
       <c r="G37" t="n">
-        <v>6.762410640716553</v>
+        <v>7.043690919876099</v>
       </c>
       <c r="H37" t="n">
-        <v>7.027734279632568</v>
+        <v>7.064640998840332</v>
       </c>
       <c r="I37" t="n">
-        <v>7.583275079727173</v>
+        <v>7.165380477905273</v>
       </c>
       <c r="J37" t="n">
-        <v>7.195784091949463</v>
+        <v>7.488540172576904</v>
       </c>
       <c r="K37" t="n">
-        <v>7.307474136352539</v>
+        <v>6.652194023132324</v>
       </c>
       <c r="L37" t="n">
-        <v>7.633326077461243</v>
+        <v>7.190181612968445</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.745452880859375</v>
+        <v>6.803292274475098</v>
       </c>
       <c r="C38" t="n">
-        <v>6.661658525466919</v>
+        <v>7.081574440002441</v>
       </c>
       <c r="D38" t="n">
-        <v>6.939474821090698</v>
+        <v>6.944462537765503</v>
       </c>
       <c r="E38" t="n">
-        <v>6.811279773712158</v>
+        <v>6.60499119758606</v>
       </c>
       <c r="F38" t="n">
-        <v>6.937970876693726</v>
+        <v>6.830591917037964</v>
       </c>
       <c r="G38" t="n">
-        <v>7.738436460494995</v>
+        <v>7.314862012863159</v>
       </c>
       <c r="H38" t="n">
-        <v>6.972389936447144</v>
+        <v>7.691789865493774</v>
       </c>
       <c r="I38" t="n">
-        <v>6.911541223526001</v>
+        <v>6.679595232009888</v>
       </c>
       <c r="J38" t="n">
-        <v>7.003060102462769</v>
+        <v>6.915518760681152</v>
       </c>
       <c r="K38" t="n">
-        <v>6.798340082168579</v>
+        <v>6.584857702255249</v>
       </c>
       <c r="L38" t="n">
-        <v>6.951960468292237</v>
+        <v>6.945153594017029</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>7.65410590171814</v>
+        <v>7.343392372131348</v>
       </c>
       <c r="C39" t="n">
-        <v>7.250649929046631</v>
+        <v>7.595214605331421</v>
       </c>
       <c r="D39" t="n">
-        <v>7.596758842468262</v>
+        <v>7.687002182006836</v>
       </c>
       <c r="E39" t="n">
-        <v>7.268578290939331</v>
+        <v>7.736868381500244</v>
       </c>
       <c r="F39" t="n">
-        <v>7.644102811813354</v>
+        <v>7.449105024337769</v>
       </c>
       <c r="G39" t="n">
-        <v>7.201266288757324</v>
+        <v>7.556246519088745</v>
       </c>
       <c r="H39" t="n">
-        <v>7.701478719711304</v>
+        <v>7.255021810531616</v>
       </c>
       <c r="I39" t="n">
-        <v>7.494009017944336</v>
+        <v>7.228576183319092</v>
       </c>
       <c r="J39" t="n">
-        <v>7.27410364151001</v>
+        <v>7.927313804626465</v>
       </c>
       <c r="K39" t="n">
-        <v>8.046976327896118</v>
+        <v>7.402156114578247</v>
       </c>
       <c r="L39" t="n">
-        <v>7.513202977180481</v>
+        <v>7.518089699745178</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>9.34320068359375</v>
+        <v>6.975218296051025</v>
       </c>
       <c r="C40" t="n">
-        <v>6.597671985626221</v>
+        <v>8.03450608253479</v>
       </c>
       <c r="D40" t="n">
-        <v>7.767200469970703</v>
+        <v>6.920882701873779</v>
       </c>
       <c r="E40" t="n">
-        <v>7.157255411148071</v>
+        <v>7.204643964767456</v>
       </c>
       <c r="F40" t="n">
-        <v>6.655550241470337</v>
+        <v>6.952755451202393</v>
       </c>
       <c r="G40" t="n">
-        <v>6.466517210006714</v>
+        <v>8.370152950286865</v>
       </c>
       <c r="H40" t="n">
-        <v>6.89795708656311</v>
+        <v>7.180732488632202</v>
       </c>
       <c r="I40" t="n">
-        <v>7.255527496337891</v>
+        <v>6.992191314697266</v>
       </c>
       <c r="J40" t="n">
-        <v>8.704350709915161</v>
+        <v>6.715389490127563</v>
       </c>
       <c r="K40" t="n">
-        <v>7.061511754989624</v>
+        <v>7.401133298873901</v>
       </c>
       <c r="L40" t="n">
-        <v>7.390674304962158</v>
+        <v>7.274760603904724</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>8.374165773391724</v>
+        <v>6.589225053787231</v>
       </c>
       <c r="C41" t="n">
-        <v>8.672438383102417</v>
+        <v>7.744788646697998</v>
       </c>
       <c r="D41" t="n">
-        <v>7.695362329483032</v>
+        <v>6.884952783584595</v>
       </c>
       <c r="E41" t="n">
-        <v>7.561773061752319</v>
+        <v>6.706907987594604</v>
       </c>
       <c r="F41" t="n">
-        <v>6.511918783187866</v>
+        <v>9.333272218704224</v>
       </c>
       <c r="G41" t="n">
-        <v>7.117436647415161</v>
+        <v>7.633561134338379</v>
       </c>
       <c r="H41" t="n">
-        <v>6.458548784255981</v>
+        <v>6.778243064880371</v>
       </c>
       <c r="I41" t="n">
-        <v>7.927318096160889</v>
+        <v>6.652555227279663</v>
       </c>
       <c r="J41" t="n">
-        <v>6.400725126266479</v>
+        <v>7.0787513256073</v>
       </c>
       <c r="K41" t="n">
-        <v>7.76622462272644</v>
+        <v>7.378811359405518</v>
       </c>
       <c r="L41" t="n">
-        <v>7.448591160774231</v>
+        <v>7.278106880187988</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>6.697437286376953</v>
+        <v>6.893600463867188</v>
       </c>
       <c r="C42" t="n">
-        <v>8.917775869369507</v>
+        <v>8.026109933853149</v>
       </c>
       <c r="D42" t="n">
-        <v>6.865537166595459</v>
+        <v>7.020769834518433</v>
       </c>
       <c r="E42" t="n">
-        <v>7.546287298202515</v>
+        <v>7.849584579467773</v>
       </c>
       <c r="F42" t="n">
-        <v>8.468950986862183</v>
+        <v>7.074079275131226</v>
       </c>
       <c r="G42" t="n">
-        <v>8.944710731506348</v>
+        <v>7.441630601882935</v>
       </c>
       <c r="H42" t="n">
-        <v>7.358752727508545</v>
+        <v>7.842636823654175</v>
       </c>
       <c r="I42" t="n">
-        <v>8.594135046005249</v>
+        <v>8.94472074508667</v>
       </c>
       <c r="J42" t="n">
-        <v>8.534768581390381</v>
+        <v>7.076601266860962</v>
       </c>
       <c r="K42" t="n">
-        <v>7.014141082763672</v>
+        <v>7.905907392501831</v>
       </c>
       <c r="L42" t="n">
-        <v>7.894249677658081</v>
+        <v>7.607564091682434</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>6.910906553268433</v>
+        <v>6.79534387588501</v>
       </c>
       <c r="C43" t="n">
-        <v>7.532651662826538</v>
+        <v>7.338438510894775</v>
       </c>
       <c r="D43" t="n">
-        <v>6.91351318359375</v>
+        <v>6.856632947921753</v>
       </c>
       <c r="E43" t="n">
-        <v>6.765392065048218</v>
+        <v>7.470550060272217</v>
       </c>
       <c r="F43" t="n">
-        <v>6.686107158660889</v>
+        <v>7.689503192901611</v>
       </c>
       <c r="G43" t="n">
-        <v>6.480125904083252</v>
+        <v>6.701878309249878</v>
       </c>
       <c r="H43" t="n">
-        <v>7.057165861129761</v>
+        <v>7.312865018844604</v>
       </c>
       <c r="I43" t="n">
-        <v>8.881883382797241</v>
+        <v>6.811645746231079</v>
       </c>
       <c r="J43" t="n">
-        <v>6.76140308380127</v>
+        <v>10.19304132461548</v>
       </c>
       <c r="K43" t="n">
-        <v>8.703304529190063</v>
+        <v>7.002108335494995</v>
       </c>
       <c r="L43" t="n">
-        <v>7.269245338439942</v>
+        <v>7.41720073223114</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.962750434875488</v>
+        <v>5.935567855834961</v>
       </c>
       <c r="C44" t="n">
-        <v>6.416664123535156</v>
+        <v>6.434479236602783</v>
       </c>
       <c r="D44" t="n">
-        <v>6.148829221725464</v>
+        <v>6.079020738601685</v>
       </c>
       <c r="E44" t="n">
-        <v>6.526425123214722</v>
+        <v>7.280457496643066</v>
       </c>
       <c r="F44" t="n">
-        <v>6.429621934890747</v>
+        <v>6.418659925460815</v>
       </c>
       <c r="G44" t="n">
-        <v>6.563782453536987</v>
+        <v>6.251559734344482</v>
       </c>
       <c r="H44" t="n">
-        <v>6.284554243087769</v>
+        <v>7.108370065689087</v>
       </c>
       <c r="I44" t="n">
-        <v>6.644104957580566</v>
+        <v>6.593205213546753</v>
       </c>
       <c r="J44" t="n">
-        <v>7.50048303604126</v>
+        <v>6.523903846740723</v>
       </c>
       <c r="K44" t="n">
-        <v>7.489475965499878</v>
+        <v>6.08200216293335</v>
       </c>
       <c r="L44" t="n">
-        <v>6.696669149398804</v>
+        <v>6.470722627639771</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>9.278403520584106</v>
+        <v>8.402606248855591</v>
       </c>
       <c r="C45" t="n">
-        <v>8.691382884979248</v>
+        <v>8.05316424369812</v>
       </c>
       <c r="D45" t="n">
-        <v>7.772194623947144</v>
+        <v>8.949233055114746</v>
       </c>
       <c r="E45" t="n">
-        <v>8.233078718185425</v>
+        <v>8.132789373397827</v>
       </c>
       <c r="F45" t="n">
-        <v>8.063518047332764</v>
+        <v>8.244992017745972</v>
       </c>
       <c r="G45" t="n">
-        <v>8.353763818740845</v>
+        <v>8.112869739532471</v>
       </c>
       <c r="H45" t="n">
-        <v>8.378180742263794</v>
+        <v>9.663349151611328</v>
       </c>
       <c r="I45" t="n">
-        <v>8.106841325759888</v>
+        <v>7.923327207565308</v>
       </c>
       <c r="J45" t="n">
-        <v>8.82649564743042</v>
+        <v>8.009079456329346</v>
       </c>
       <c r="K45" t="n">
-        <v>7.561240673065186</v>
+        <v>7.732325315475464</v>
       </c>
       <c r="L45" t="n">
-        <v>8.326510000228883</v>
+        <v>8.322373580932616</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.090934276580811</v>
+        <v>6.869507551193237</v>
       </c>
       <c r="C46" t="n">
-        <v>6.979230642318726</v>
+        <v>7.555743217468262</v>
       </c>
       <c r="D46" t="n">
-        <v>6.67000675201416</v>
+        <v>6.368256330490112</v>
       </c>
       <c r="E46" t="n">
-        <v>9.425010681152344</v>
+        <v>7.374220132827759</v>
       </c>
       <c r="F46" t="n">
-        <v>6.530386209487915</v>
+        <v>6.772329330444336</v>
       </c>
       <c r="G46" t="n">
-        <v>7.513360500335693</v>
+        <v>7.049046993255615</v>
       </c>
       <c r="H46" t="n">
-        <v>6.867498159408569</v>
+        <v>6.730336427688599</v>
       </c>
       <c r="I46" t="n">
-        <v>7.791148662567139</v>
+        <v>6.684459209442139</v>
       </c>
       <c r="J46" t="n">
-        <v>7.47093939781189</v>
+        <v>7.01911473274231</v>
       </c>
       <c r="K46" t="n">
-        <v>8.596102237701416</v>
+        <v>7.927324056625366</v>
       </c>
       <c r="L46" t="n">
-        <v>7.493461751937867</v>
+        <v>7.035033798217773</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.00065016746521</v>
+        <v>7.65247917175293</v>
       </c>
       <c r="C47" t="n">
-        <v>7.843023538589478</v>
+        <v>9.393099784851074</v>
       </c>
       <c r="D47" t="n">
-        <v>8.384650945663452</v>
+        <v>8.835497140884399</v>
       </c>
       <c r="E47" t="n">
-        <v>10.38303375244141</v>
+        <v>9.989546775817871</v>
       </c>
       <c r="F47" t="n">
-        <v>7.5797119140625</v>
+        <v>8.592137813568115</v>
       </c>
       <c r="G47" t="n">
-        <v>7.535304069519043</v>
+        <v>7.968168497085571</v>
       </c>
       <c r="H47" t="n">
-        <v>9.971628665924072</v>
+        <v>9.091335773468018</v>
       </c>
       <c r="I47" t="n">
-        <v>7.897856473922729</v>
+        <v>8.438632011413574</v>
       </c>
       <c r="J47" t="n">
-        <v>9.075418710708618</v>
+        <v>8.102899789810181</v>
       </c>
       <c r="K47" t="n">
-        <v>7.819092750549316</v>
+        <v>7.982142448425293</v>
       </c>
       <c r="L47" t="n">
-        <v>8.449037098884583</v>
+        <v>8.604593920707703</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>6.443580150604248</v>
+        <v>6.715414524078369</v>
       </c>
       <c r="C48" t="n">
-        <v>6.198225259780884</v>
+        <v>7.051036834716797</v>
       </c>
       <c r="D48" t="n">
-        <v>7.293947219848633</v>
+        <v>5.823174476623535</v>
       </c>
       <c r="E48" t="n">
-        <v>6.302461385726929</v>
+        <v>6.642068862915039</v>
       </c>
       <c r="F48" t="n">
-        <v>6.385728359222412</v>
+        <v>6.667500734329224</v>
       </c>
       <c r="G48" t="n">
-        <v>6.314424753189087</v>
+        <v>6.214167594909668</v>
       </c>
       <c r="H48" t="n">
-        <v>6.174758911132812</v>
+        <v>5.995724439620972</v>
       </c>
       <c r="I48" t="n">
-        <v>6.81365180015564</v>
+        <v>7.655507802963257</v>
       </c>
       <c r="J48" t="n">
-        <v>6.219181776046753</v>
+        <v>6.473013401031494</v>
       </c>
       <c r="K48" t="n">
-        <v>5.717938184738159</v>
+        <v>7.405636548995972</v>
       </c>
       <c r="L48" t="n">
-        <v>6.386389780044555</v>
+        <v>6.664324522018433</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.243068695068359</v>
+        <v>6.683964014053345</v>
       </c>
       <c r="C49" t="n">
-        <v>7.616077899932861</v>
+        <v>7.375223159790039</v>
       </c>
       <c r="D49" t="n">
-        <v>7.223137140274048</v>
+        <v>7.021141767501831</v>
       </c>
       <c r="E49" t="n">
-        <v>8.221059083938599</v>
+        <v>8.00461745262146</v>
       </c>
       <c r="F49" t="n">
-        <v>6.5727379322052</v>
+        <v>6.706417560577393</v>
       </c>
       <c r="G49" t="n">
-        <v>7.07056736946106</v>
+        <v>7.047044277191162</v>
       </c>
       <c r="H49" t="n">
-        <v>7.207653045654297</v>
+        <v>6.751318216323853</v>
       </c>
       <c r="I49" t="n">
-        <v>6.493444681167603</v>
+        <v>6.987198352813721</v>
       </c>
       <c r="J49" t="n">
-        <v>7.112364530563354</v>
+        <v>6.873034000396729</v>
       </c>
       <c r="K49" t="n">
-        <v>6.681525945663452</v>
+        <v>7.017098188400269</v>
       </c>
       <c r="L49" t="n">
-        <v>7.144163632392884</v>
+        <v>7.04670569896698</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>9.280910491943359</v>
+        <v>7.403178691864014</v>
       </c>
       <c r="C50" t="n">
-        <v>7.440062522888184</v>
+        <v>7.564222097396851</v>
       </c>
       <c r="D50" t="n">
-        <v>8.722276449203491</v>
+        <v>7.012171745300293</v>
       </c>
       <c r="E50" t="n">
-        <v>7.979691982269287</v>
+        <v>7.609583377838135</v>
       </c>
       <c r="F50" t="n">
-        <v>9.132267475128174</v>
+        <v>7.538312196731567</v>
       </c>
       <c r="G50" t="n">
-        <v>7.093910455703735</v>
+        <v>7.52832555770874</v>
       </c>
       <c r="H50" t="n">
-        <v>8.474910736083984</v>
+        <v>7.423106908798218</v>
       </c>
       <c r="I50" t="n">
-        <v>7.314871549606323</v>
+        <v>7.924332857131958</v>
       </c>
       <c r="J50" t="n">
-        <v>7.13537073135376</v>
+        <v>9.310832738876343</v>
       </c>
       <c r="K50" t="n">
-        <v>8.642002582550049</v>
+        <v>8.318319082260132</v>
       </c>
       <c r="L50" t="n">
-        <v>8.121627497673035</v>
+        <v>7.763238525390625</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>6.878017902374268</v>
+        <v>6.772767066955566</v>
       </c>
       <c r="C51" t="n">
-        <v>7.703212261199951</v>
+        <v>7.425090551376343</v>
       </c>
       <c r="D51" t="n">
-        <v>7.36737585067749</v>
+        <v>7.248527526855469</v>
       </c>
       <c r="E51" t="n">
-        <v>6.963912487030029</v>
+        <v>6.73033881187439</v>
       </c>
       <c r="F51" t="n">
-        <v>6.734996557235718</v>
+        <v>6.530393600463867</v>
       </c>
       <c r="G51" t="n">
-        <v>8.887691259384155</v>
+        <v>6.576732635498047</v>
       </c>
       <c r="H51" t="n">
-        <v>6.546725511550903</v>
+        <v>6.586218118667603</v>
       </c>
       <c r="I51" t="n">
-        <v>6.523867845535278</v>
+        <v>6.822634935379028</v>
       </c>
       <c r="J51" t="n">
-        <v>8.045489072799683</v>
+        <v>6.438601016998291</v>
       </c>
       <c r="K51" t="n">
-        <v>7.169784784317017</v>
+        <v>7.357281446456909</v>
       </c>
       <c r="L51" t="n">
-        <v>7.282107353210449</v>
+        <v>6.848858571052551</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.728406653404236</v>
+        <v>7.560607891082764</v>
       </c>
       <c r="C52" t="n">
-        <v>7.710192670822144</v>
+        <v>7.567249536514282</v>
       </c>
       <c r="D52" t="n">
-        <v>7.644352197647095</v>
+        <v>7.653111338615417</v>
       </c>
       <c r="E52" t="n">
-        <v>7.942522511482239</v>
+        <v>7.663086576461792</v>
       </c>
       <c r="F52" t="n">
-        <v>7.615360770225525</v>
+        <v>7.595954260826111</v>
       </c>
       <c r="G52" t="n">
-        <v>7.480273895263672</v>
+        <v>7.531234707832336</v>
       </c>
       <c r="H52" t="n">
-        <v>7.579010949134827</v>
+        <v>7.514003405570984</v>
       </c>
       <c r="I52" t="n">
-        <v>7.623285212516785</v>
+        <v>7.474267182350158</v>
       </c>
       <c r="J52" t="n">
-        <v>7.597023482322693</v>
+        <v>7.668700914382935</v>
       </c>
       <c r="K52" t="n">
-        <v>7.560563569068909</v>
+        <v>7.643146214485168</v>
       </c>
       <c r="L52" t="n">
-        <v>7.648099191188813</v>
+        <v>7.587136202812195</v>
       </c>
     </row>
   </sheetData>
